--- a/docs/d/231/inyear.xlsx
+++ b/docs/d/231/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 22-Sep-2026. Built 2026-09-23 09:04 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:13 PDT.</t>
         </is>
       </c>
     </row>
@@ -588,7 +588,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (189 days) - 62 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (189 days) - 61 clubs short</t>
         </is>
       </c>
     </row>
@@ -8693,7 +8693,7 @@
         </is>
       </c>
       <c r="E83" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F83" s="6" t="n">
         <v>10</v>
@@ -8707,13 +8707,13 @@
         </is>
       </c>
       <c r="I83" s="4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J83" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K83" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L83" s="4" t="inlineStr">
         <is>
@@ -8751,8 +8751,8 @@
       <c r="U83" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V83" s="9" t="n">
-        <v>3</v>
+      <c r="V83" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W83" s="9" t="n">
         <v>0</v>
@@ -9316,7 +9316,7 @@
         </is>
       </c>
       <c r="P89" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q89" s="9" t="n">
         <v>0</v>
@@ -10868,7 +10868,7 @@
         </is>
       </c>
       <c r="P105" s="10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q105" s="10" t="n">
         <v>2</v>
@@ -11603,7 +11603,7 @@
         </is>
       </c>
       <c r="E113" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F113" s="6" t="n">
         <v>10</v>
@@ -11673,8 +11673,8 @@
       <c r="Y113" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z113" s="9" t="n">
-        <v>0</v>
+      <c r="Z113" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA113" s="10" t="n">
         <v>1</v>
@@ -12711,13 +12711,13 @@
         </is>
       </c>
       <c r="P124" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q124" s="10" t="n">
         <v>2</v>
       </c>
       <c r="R124" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S124" s="9" t="n">
         <v>0</v>
@@ -16401,7 +16401,7 @@
         <v>5</v>
       </c>
       <c r="D16" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -16599,7 +16599,7 @@
         <v>4</v>
       </c>
       <c r="D22" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>

--- a/docs/d/231/inyear.xlsx
+++ b/docs/d/231/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:13 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:41 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/231/inyear.xlsx
+++ b/docs/d/231/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:41 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 26-Sep-2026. Built 2026-09-27 12:40 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>280 days remain until 30 June 2027, when these scores become final.</t>
+          <t>276 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (99 days) - 7 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (95 days) - 7 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (158 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (154 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (189 days) - 61 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (185 days) - 53 clubs short</t>
         </is>
       </c>
     </row>
@@ -1127,7 +1127,7 @@
         </is>
       </c>
       <c r="E5" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F5" s="6" t="n">
         <v>10</v>
@@ -1170,8 +1170,8 @@
       <c r="P5" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="Q5" s="9" t="n">
-        <v>1</v>
+      <c r="Q5" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R5" s="9" t="n">
         <v>0</v>
@@ -1612,7 +1612,7 @@
         </is>
       </c>
       <c r="E10" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F10" s="6" t="n">
         <v>10</v>
@@ -1682,8 +1682,8 @@
       <c r="Y10" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z10" s="9" t="n">
-        <v>0</v>
+      <c r="Z10" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA10" s="10" t="n">
         <v>1</v>
@@ -3108,7 +3108,7 @@
         </is>
       </c>
       <c r="P25" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q25" s="9" t="n">
         <v>0</v>
@@ -3358,7 +3358,7 @@
         </is>
       </c>
       <c r="E28" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F28" s="6" t="n">
         <v>10</v>
@@ -3428,8 +3428,8 @@
       <c r="Y28" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z28" s="9" t="n">
-        <v>0</v>
+      <c r="Z28" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="AA28" s="10" t="n">
         <v>1</v>
@@ -3802,7 +3802,7 @@
         <v>1</v>
       </c>
       <c r="U32" s="10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V32" s="10" t="n">
         <v>4</v>
@@ -7820,7 +7820,7 @@
         </is>
       </c>
       <c r="E74" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F74" s="6" t="n">
         <v>10</v>
@@ -7890,8 +7890,8 @@
       <c r="Y74" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z74" s="9" t="n">
-        <v>0</v>
+      <c r="Z74" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA74" s="10" t="n">
         <v>1</v>
@@ -9319,7 +9319,7 @@
         <v>2</v>
       </c>
       <c r="Q89" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R89" s="9" t="n">
         <v>0</v>
@@ -9372,7 +9372,7 @@
         </is>
       </c>
       <c r="E90" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F90" s="6" t="n">
         <v>10</v>
@@ -9442,8 +9442,8 @@
       <c r="Y90" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z90" s="9" t="n">
-        <v>0</v>
+      <c r="Z90" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA90" s="10" t="n">
         <v>1</v>
@@ -10051,7 +10051,7 @@
         </is>
       </c>
       <c r="E97" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F97" s="6" t="n">
         <v>10</v>
@@ -10065,13 +10065,13 @@
         </is>
       </c>
       <c r="I97" s="4" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="J97" s="4" t="n">
         <v>35</v>
       </c>
       <c r="K97" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L97" s="4" t="inlineStr">
         <is>
@@ -10109,8 +10109,8 @@
       <c r="U97" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="V97" s="9" t="n">
-        <v>3</v>
+      <c r="V97" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W97" s="9" t="n">
         <v>0</v>
@@ -10245,7 +10245,7 @@
         </is>
       </c>
       <c r="E99" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F99" s="6" t="n">
         <v>10</v>
@@ -10315,8 +10315,8 @@
       <c r="Y99" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z99" s="9" t="n">
-        <v>0</v>
+      <c r="Z99" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA99" s="10" t="n">
         <v>1</v>
@@ -10924,7 +10924,7 @@
         </is>
       </c>
       <c r="E106" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F106" s="6" t="n">
         <v>10</v>
@@ -10994,8 +10994,8 @@
       <c r="Y106" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z106" s="9" t="n">
-        <v>0</v>
+      <c r="Z106" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA106" s="10" t="n">
         <v>1</v>
@@ -11215,7 +11215,7 @@
         </is>
       </c>
       <c r="E109" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F109" s="6" t="n">
         <v>10</v>
@@ -11267,8 +11267,8 @@
       <c r="S109" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T109" s="9" t="n">
-        <v>0</v>
+      <c r="T109" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U109" s="9" t="n">
         <v>0</v>
@@ -11811,13 +11811,13 @@
         </is>
       </c>
       <c r="I115" s="4" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="J115" s="4" t="n">
         <v>51</v>
       </c>
       <c r="K115" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L115" s="4" t="inlineStr">
         <is>
@@ -11856,7 +11856,7 @@
         <v>0</v>
       </c>
       <c r="V115" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W115" s="9" t="n">
         <v>0</v>
@@ -11991,7 +11991,7 @@
         </is>
       </c>
       <c r="E117" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F117" s="6" t="n">
         <v>10</v>
@@ -12061,8 +12061,8 @@
       <c r="Y117" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z117" s="9" t="n">
-        <v>0</v>
+      <c r="Z117" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA117" s="10" t="n">
         <v>1</v>
@@ -12573,7 +12573,7 @@
         </is>
       </c>
       <c r="E123" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F123" s="6" t="n">
         <v>10</v>
@@ -12617,13 +12617,13 @@
         <v>3</v>
       </c>
       <c r="Q123" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R123" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S123" s="9" t="n">
-        <v>1</v>
+      <c r="S123" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="T123" s="9" t="n">
         <v>0</v>
@@ -13058,7 +13058,7 @@
         </is>
       </c>
       <c r="E128" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F128" s="6" t="n">
         <v>10</v>
@@ -13128,8 +13128,8 @@
       <c r="Y128" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z128" s="9" t="n">
-        <v>0</v>
+      <c r="Z128" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA128" s="10" t="n">
         <v>1</v>
@@ -13296,7 +13296,7 @@
         <v>2</v>
       </c>
       <c r="Q130" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R130" s="9" t="n">
         <v>0</v>
@@ -15774,7 +15774,7 @@
         </is>
       </c>
       <c r="E156" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F156" s="6" t="n">
         <v>10</v>
@@ -15817,8 +15817,8 @@
       <c r="P156" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="Q156" s="9" t="n">
-        <v>0</v>
+      <c r="Q156" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R156" s="9" t="n">
         <v>0</v>
@@ -15939,7 +15939,7 @@
         <v>6</v>
       </c>
       <c r="D2" t="n">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -15972,7 +15972,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="E3" t="n">
         <v>1</v>
@@ -16071,7 +16071,7 @@
         <v>6</v>
       </c>
       <c r="D6" t="n">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -16335,7 +16335,7 @@
         <v>6</v>
       </c>
       <c r="D14" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -16467,7 +16467,7 @@
         <v>6</v>
       </c>
       <c r="D18" t="n">
-        <v>0.67</v>
+        <v>0.83</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -16500,7 +16500,7 @@
         <v>6</v>
       </c>
       <c r="D19" t="n">
-        <v>1.67</v>
+        <v>2</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
@@ -16533,7 +16533,7 @@
         <v>5</v>
       </c>
       <c r="D20" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
@@ -16566,7 +16566,7 @@
         <v>5</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
@@ -16632,7 +16632,7 @@
         <v>4</v>
       </c>
       <c r="D23" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
@@ -16665,7 +16665,7 @@
         <v>5</v>
       </c>
       <c r="D24" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
@@ -16698,7 +16698,7 @@
         <v>5</v>
       </c>
       <c r="D25" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="E25" t="n">
         <v>0</v>
@@ -16863,7 +16863,7 @@
         <v>5</v>
       </c>
       <c r="D30" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="E30" t="n">
         <v>0</v>

--- a/docs/d/231/inyear.xlsx
+++ b/docs/d/231/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 26-Sep-2026. Built 2026-09-27 12:40 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 03-Oct-2026. Built 2026-10-04 12:23 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>276 days remain until 30 June 2027, when these scores become final.</t>
+          <t>269 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (95 days) - 7 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (88 days) - 7 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (154 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (147 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (185 days) - 53 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (178 days) - 28 clubs short</t>
         </is>
       </c>
     </row>
@@ -2000,7 +2000,7 @@
         </is>
       </c>
       <c r="E14" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F14" s="6" t="n">
         <v>10</v>
@@ -2070,8 +2070,8 @@
       <c r="Y14" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z14" s="9" t="n">
-        <v>0</v>
+      <c r="Z14" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA14" s="10" t="n">
         <v>1</v>
@@ -2141,7 +2141,7 @@
         <v>1</v>
       </c>
       <c r="Q15" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R15" s="9" t="n">
         <v>0</v>
@@ -2194,7 +2194,7 @@
         </is>
       </c>
       <c r="E16" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F16" s="6" t="n">
         <v>10</v>
@@ -2264,8 +2264,8 @@
       <c r="Y16" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z16" s="9" t="n">
-        <v>0</v>
+      <c r="Z16" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA16" s="10" t="n">
         <v>1</v>
@@ -2817,7 +2817,7 @@
         </is>
       </c>
       <c r="P22" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Q22" s="9" t="n">
         <v>1</v>
@@ -2914,7 +2914,7 @@
         </is>
       </c>
       <c r="P23" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q23" s="9" t="n">
         <v>1</v>
@@ -2970,7 +2970,7 @@
         </is>
       </c>
       <c r="E24" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F24" s="6" t="n">
         <v>10</v>
@@ -3040,8 +3040,8 @@
       <c r="Y24" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z24" s="9" t="n">
-        <v>0</v>
+      <c r="Z24" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA24" s="10" t="n">
         <v>1</v>
@@ -3372,13 +3372,13 @@
         </is>
       </c>
       <c r="I28" s="4" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="J28" s="4" t="n">
         <v>23</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L28" s="4" t="inlineStr">
         <is>
@@ -3417,7 +3417,7 @@
         <v>0</v>
       </c>
       <c r="V28" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W28" s="9" t="n">
         <v>0</v>
@@ -3455,7 +3455,7 @@
         </is>
       </c>
       <c r="E29" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F29" s="6" t="n">
         <v>10</v>
@@ -3525,8 +3525,8 @@
       <c r="Y29" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z29" s="9" t="n">
-        <v>0</v>
+      <c r="Z29" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA29" s="10" t="n">
         <v>1</v>
@@ -3552,7 +3552,7 @@
         </is>
       </c>
       <c r="E30" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F30" s="6" t="n">
         <v>10</v>
@@ -3622,8 +3622,8 @@
       <c r="Y30" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z30" s="9" t="n">
-        <v>0</v>
+      <c r="Z30" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA30" s="10" t="n">
         <v>1</v>
@@ -4910,7 +4910,7 @@
         </is>
       </c>
       <c r="E44" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F44" s="6" t="n">
         <v>10</v>
@@ -4980,8 +4980,8 @@
       <c r="Y44" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z44" s="9" t="n">
-        <v>0</v>
+      <c r="Z44" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA44" s="10" t="n">
         <v>1</v>
@@ -5201,7 +5201,7 @@
         </is>
       </c>
       <c r="E47" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F47" s="6" t="n">
         <v>10</v>
@@ -5271,8 +5271,8 @@
       <c r="Y47" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z47" s="9" t="n">
-        <v>0</v>
+      <c r="Z47" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA47" s="10" t="n">
         <v>1</v>
@@ -5686,7 +5686,7 @@
         </is>
       </c>
       <c r="E52" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F52" s="6" t="n">
         <v>10</v>
@@ -5756,8 +5756,8 @@
       <c r="Y52" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z52" s="9" t="n">
-        <v>0</v>
+      <c r="Z52" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA52" s="10" t="n">
         <v>1</v>
@@ -5880,7 +5880,7 @@
         </is>
       </c>
       <c r="E54" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F54" s="6" t="n">
         <v>10</v>
@@ -5950,8 +5950,8 @@
       <c r="Y54" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z54" s="9" t="n">
-        <v>0</v>
+      <c r="Z54" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA54" s="10" t="n">
         <v>1</v>
@@ -6018,7 +6018,7 @@
         </is>
       </c>
       <c r="P55" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q55" s="9" t="n">
         <v>0</v>
@@ -6171,7 +6171,7 @@
         </is>
       </c>
       <c r="E57" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F57" s="6" t="n">
         <v>10</v>
@@ -6241,8 +6241,8 @@
       <c r="Y57" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z57" s="9" t="n">
-        <v>0</v>
+      <c r="Z57" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA57" s="10" t="n">
         <v>1</v>
@@ -6379,13 +6379,13 @@
         </is>
       </c>
       <c r="I59" s="4" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J59" s="4" t="n">
         <v>33</v>
       </c>
       <c r="K59" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L59" s="4" t="inlineStr">
         <is>
@@ -6424,7 +6424,7 @@
         <v>3</v>
       </c>
       <c r="V59" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W59" s="9" t="n">
         <v>0</v>
@@ -6462,7 +6462,7 @@
         </is>
       </c>
       <c r="E60" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F60" s="6" t="n">
         <v>10</v>
@@ -6532,8 +6532,8 @@
       <c r="Y60" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z60" s="9" t="n">
-        <v>0</v>
+      <c r="Z60" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA60" s="10" t="n">
         <v>1</v>
@@ -6753,7 +6753,7 @@
         </is>
       </c>
       <c r="E63" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F63" s="6" t="n">
         <v>10</v>
@@ -6823,8 +6823,8 @@
       <c r="Y63" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z63" s="9" t="n">
-        <v>0</v>
+      <c r="Z63" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA63" s="10" t="n">
         <v>1</v>
@@ -6947,7 +6947,7 @@
         </is>
       </c>
       <c r="E65" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F65" s="6" t="n">
         <v>10</v>
@@ -7017,8 +7017,8 @@
       <c r="Y65" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z65" s="9" t="n">
-        <v>0</v>
+      <c r="Z65" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA65" s="10" t="n">
         <v>1</v>
@@ -7579,7 +7579,7 @@
         <v>0</v>
       </c>
       <c r="S71" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T71" s="9" t="n">
         <v>0</v>
@@ -8014,7 +8014,7 @@
         </is>
       </c>
       <c r="E76" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F76" s="6" t="n">
         <v>10</v>
@@ -8084,8 +8084,8 @@
       <c r="Y76" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z76" s="9" t="n">
-        <v>0</v>
+      <c r="Z76" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA76" s="10" t="n">
         <v>1</v>
@@ -8416,13 +8416,13 @@
         </is>
       </c>
       <c r="I80" s="4" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J80" s="4" t="n">
         <v>29</v>
       </c>
       <c r="K80" s="4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L80" s="4" t="inlineStr">
         <is>
@@ -8464,7 +8464,7 @@
         <v>4</v>
       </c>
       <c r="W80" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="X80" s="10" t="n">
         <v>5</v>
@@ -8790,7 +8790,7 @@
         </is>
       </c>
       <c r="E84" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F84" s="6" t="n">
         <v>10</v>
@@ -8804,13 +8804,13 @@
         </is>
       </c>
       <c r="I84" s="4" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="J84" s="4" t="n">
         <v>28</v>
       </c>
       <c r="K84" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L84" s="4" t="inlineStr">
         <is>
@@ -8833,8 +8833,8 @@
       <c r="P84" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="Q84" s="9" t="n">
-        <v>1</v>
+      <c r="Q84" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R84" s="9" t="n">
         <v>0</v>
@@ -8852,7 +8852,7 @@
         <v>4</v>
       </c>
       <c r="W84" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X84" s="10" t="n">
         <v>7</v>
@@ -8901,17 +8901,17 @@
         </is>
       </c>
       <c r="I85" s="4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J85" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K85" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="L85" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>5</v>
+      </c>
+      <c r="L85" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M85" s="8" t="n">
@@ -8949,7 +8949,7 @@
         <v>4</v>
       </c>
       <c r="W85" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X85" s="10" t="n">
         <v>4</v>
@@ -9025,7 +9025,7 @@
         </is>
       </c>
       <c r="P86" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q86" s="9" t="n">
         <v>0</v>
@@ -10536,7 +10536,7 @@
         </is>
       </c>
       <c r="E102" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F102" s="6" t="n">
         <v>10</v>
@@ -10606,8 +10606,8 @@
       <c r="Y102" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z102" s="9" t="n">
-        <v>0</v>
+      <c r="Z102" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA102" s="10" t="n">
         <v>1</v>
@@ -11312,7 +11312,7 @@
         </is>
       </c>
       <c r="E110" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F110" s="6" t="n">
         <v>10</v>
@@ -11382,8 +11382,8 @@
       <c r="Y110" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z110" s="9" t="n">
-        <v>0</v>
+      <c r="Z110" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA110" s="10" t="n">
         <v>1</v>
@@ -11409,7 +11409,7 @@
         </is>
       </c>
       <c r="E111" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F111" s="6" t="n">
         <v>10</v>
@@ -11479,8 +11479,8 @@
       <c r="Y111" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z111" s="9" t="n">
-        <v>0</v>
+      <c r="Z111" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA111" s="10" t="n">
         <v>1</v>
@@ -12379,7 +12379,7 @@
         </is>
       </c>
       <c r="E121" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F121" s="6" t="n">
         <v>10</v>
@@ -12420,7 +12420,7 @@
         </is>
       </c>
       <c r="P121" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q121" s="9" t="n">
         <v>0</v>
@@ -12428,8 +12428,8 @@
       <c r="R121" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S121" s="9" t="n">
-        <v>1</v>
+      <c r="S121" s="10" t="n">
+        <v>3</v>
       </c>
       <c r="T121" s="9" t="n">
         <v>0</v>
@@ -12864,7 +12864,7 @@
         </is>
       </c>
       <c r="E126" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F126" s="6" t="n">
         <v>10</v>
@@ -12934,8 +12934,8 @@
       <c r="Y126" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z126" s="9" t="n">
-        <v>0</v>
+      <c r="Z126" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA126" s="10" t="n">
         <v>1</v>
@@ -13155,7 +13155,7 @@
         </is>
       </c>
       <c r="E129" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F129" s="6" t="n">
         <v>10</v>
@@ -13225,8 +13225,8 @@
       <c r="Y129" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z129" s="9" t="n">
-        <v>0</v>
+      <c r="Z129" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA129" s="10" t="n">
         <v>1</v>
@@ -13252,7 +13252,7 @@
         </is>
       </c>
       <c r="E130" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F130" s="6" t="n">
         <v>10</v>
@@ -13322,8 +13322,8 @@
       <c r="Y130" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z130" s="9" t="n">
-        <v>0</v>
+      <c r="Z130" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA130" s="10" t="n">
         <v>1</v>
@@ -13543,7 +13543,7 @@
         </is>
       </c>
       <c r="E133" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F133" s="6" t="n">
         <v>10</v>
@@ -13587,7 +13587,7 @@
         <v>0</v>
       </c>
       <c r="Q133" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R133" s="9" t="n">
         <v>0</v>
@@ -13595,8 +13595,8 @@
       <c r="S133" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T133" s="9" t="n">
-        <v>0</v>
+      <c r="T133" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U133" s="9" t="n">
         <v>0</v>
@@ -13737,7 +13737,7 @@
         </is>
       </c>
       <c r="E135" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F135" s="6" t="n">
         <v>10</v>
@@ -13807,8 +13807,8 @@
       <c r="Y135" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z135" s="9" t="n">
-        <v>0</v>
+      <c r="Z135" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA135" s="10" t="n">
         <v>1</v>
@@ -13834,7 +13834,7 @@
         </is>
       </c>
       <c r="E136" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F136" s="6" t="n">
         <v>10</v>
@@ -13904,8 +13904,8 @@
       <c r="Y136" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z136" s="9" t="n">
-        <v>0</v>
+      <c r="Z136" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA136" s="10" t="n">
         <v>1</v>
@@ -14125,7 +14125,7 @@
         </is>
       </c>
       <c r="E139" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F139" s="6" t="n">
         <v>10</v>
@@ -14195,8 +14195,8 @@
       <c r="Y139" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z139" s="9" t="n">
-        <v>0</v>
+      <c r="Z139" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA139" s="10" t="n">
         <v>1</v>
@@ -14319,7 +14319,7 @@
         </is>
       </c>
       <c r="E141" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F141" s="6" t="n">
         <v>10</v>
@@ -14389,8 +14389,8 @@
       <c r="Y141" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z141" s="9" t="n">
-        <v>0</v>
+      <c r="Z141" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA141" s="10" t="n">
         <v>1</v>
@@ -14457,7 +14457,7 @@
         </is>
       </c>
       <c r="P142" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q142" s="9" t="n">
         <v>0</v>
@@ -14721,13 +14721,13 @@
         </is>
       </c>
       <c r="I145" s="4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J145" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K145" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L145" s="7" t="inlineStr">
         <is>
@@ -14766,7 +14766,7 @@
         <v>0</v>
       </c>
       <c r="V145" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W145" s="9" t="n">
         <v>0</v>
@@ -15774,7 +15774,7 @@
         </is>
       </c>
       <c r="E156" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F156" s="6" t="n">
         <v>10</v>
@@ -15844,8 +15844,8 @@
       <c r="Y156" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z156" s="9" t="n">
-        <v>0</v>
+      <c r="Z156" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA156" s="10" t="n">
         <v>1</v>
@@ -16005,7 +16005,7 @@
         <v>6</v>
       </c>
       <c r="D4" t="n">
-        <v>1.5</v>
+        <v>1.83</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -16038,7 +16038,7 @@
         <v>6</v>
       </c>
       <c r="D5" t="n">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -16071,7 +16071,7 @@
         <v>6</v>
       </c>
       <c r="D6" t="n">
-        <v>1</v>
+        <v>1.33</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -16170,7 +16170,7 @@
         <v>5</v>
       </c>
       <c r="D9" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -16203,7 +16203,7 @@
         <v>5</v>
       </c>
       <c r="D10" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -16236,7 +16236,7 @@
         <v>6</v>
       </c>
       <c r="D11" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -16269,7 +16269,7 @@
         <v>6</v>
       </c>
       <c r="D12" t="n">
-        <v>1.5</v>
+        <v>1.83</v>
       </c>
       <c r="E12" t="n">
         <v>1</v>
@@ -16302,7 +16302,7 @@
         <v>5</v>
       </c>
       <c r="D13" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -16368,7 +16368,7 @@
         <v>4</v>
       </c>
       <c r="D15" t="n">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -16434,7 +16434,7 @@
         <v>6</v>
       </c>
       <c r="D17" t="n">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -16449,7 +16449,7 @@
         <v>0</v>
       </c>
       <c r="I17" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="18">
@@ -16533,7 +16533,7 @@
         <v>5</v>
       </c>
       <c r="D20" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
@@ -16566,7 +16566,7 @@
         <v>5</v>
       </c>
       <c r="D21" t="n">
-        <v>0.2</v>
+        <v>0.6</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
@@ -16665,7 +16665,7 @@
         <v>5</v>
       </c>
       <c r="D24" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
@@ -16698,7 +16698,7 @@
         <v>5</v>
       </c>
       <c r="D25" t="n">
-        <v>1.2</v>
+        <v>1.6</v>
       </c>
       <c r="E25" t="n">
         <v>0</v>
@@ -16731,7 +16731,7 @@
         <v>5</v>
       </c>
       <c r="D26" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="E26" t="n">
         <v>0</v>
@@ -16764,7 +16764,7 @@
         <v>6</v>
       </c>
       <c r="D27" t="n">
-        <v>1.17</v>
+        <v>1.67</v>
       </c>
       <c r="E27" t="n">
         <v>0</v>
@@ -16797,7 +16797,7 @@
         <v>6</v>
       </c>
       <c r="D28" t="n">
-        <v>0.67</v>
+        <v>0.83</v>
       </c>
       <c r="E28" t="n">
         <v>0</v>
@@ -16863,7 +16863,7 @@
         <v>5</v>
       </c>
       <c r="D30" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="E30" t="n">
         <v>0</v>

--- a/docs/d/231/inyear.xlsx
+++ b/docs/d/231/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 03-Oct-2026. Built 2026-10-04 12:23 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 08:33 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>269 days remain until 30 June 2027, when these scores become final.</t>
+          <t>262 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (88 days) - 7 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (81 days) - 7 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (147 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (140 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (178 days) - 28 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (171 days) - 27 clubs short</t>
         </is>
       </c>
     </row>
@@ -850,13 +850,13 @@
         </is>
       </c>
       <c r="I2" s="4" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="J2" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K2" s="4" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="L2" s="7" t="inlineStr">
         <is>
@@ -933,7 +933,7 @@
         </is>
       </c>
       <c r="E3" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F3" s="6" t="n">
         <v>10</v>
@@ -947,13 +947,13 @@
         </is>
       </c>
       <c r="I3" s="4" t="n">
-        <v>37</v>
+        <v>22</v>
       </c>
       <c r="J3" s="4" t="n">
         <v>35</v>
       </c>
       <c r="K3" s="4" t="n">
-        <v>2</v>
+        <v>-13</v>
       </c>
       <c r="L3" s="4" t="inlineStr">
         <is>
@@ -991,8 +991,8 @@
       <c r="U3" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V3" s="9" t="n">
-        <v>2</v>
+      <c r="V3" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W3" s="9" t="n">
         <v>0</v>
@@ -1030,7 +1030,7 @@
         </is>
       </c>
       <c r="E4" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F4" s="6" t="n">
         <v>10</v>
@@ -1044,13 +1044,13 @@
         </is>
       </c>
       <c r="I4" s="4" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="J4" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K4" s="4" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="L4" s="4" t="inlineStr">
         <is>
@@ -1091,8 +1091,8 @@
       <c r="V4" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W4" s="9" t="n">
-        <v>2</v>
+      <c r="W4" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="X4" s="10" t="n">
         <v>6</v>
@@ -1127,7 +1127,7 @@
         </is>
       </c>
       <c r="E5" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F5" s="6" t="n">
         <v>10</v>
@@ -1185,8 +1185,8 @@
       <c r="U5" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V5" s="9" t="n">
-        <v>3</v>
+      <c r="V5" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W5" s="9" t="n">
         <v>0</v>
@@ -1238,13 +1238,13 @@
         </is>
       </c>
       <c r="I6" s="4" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="J6" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="L6" s="7" t="inlineStr">
         <is>
@@ -1335,13 +1335,13 @@
         </is>
       </c>
       <c r="I7" s="4" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="J7" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>0</v>
+        <v>-9</v>
       </c>
       <c r="L7" s="7" t="inlineStr">
         <is>
@@ -1365,7 +1365,7 @@
         <v>1</v>
       </c>
       <c r="Q7" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R7" s="9" t="n">
         <v>0</v>
@@ -1432,17 +1432,17 @@
         </is>
       </c>
       <c r="I8" s="4" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J8" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-20</v>
+      </c>
+      <c r="L8" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M8" s="8" t="n">
@@ -1529,13 +1529,13 @@
         </is>
       </c>
       <c r="I9" s="4" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="J9" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>0</v>
+        <v>-9</v>
       </c>
       <c r="L9" s="7" t="inlineStr">
         <is>
@@ -1626,17 +1626,17 @@
         </is>
       </c>
       <c r="I10" s="4" t="n">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="J10" s="4" t="n">
         <v>31</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-18</v>
+      </c>
+      <c r="L10" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M10" s="8" t="n">
@@ -1723,17 +1723,17 @@
         </is>
       </c>
       <c r="I11" s="4" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="J11" s="4" t="n">
         <v>19</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="L11" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>0</v>
+      </c>
+      <c r="L11" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M11" s="8" t="n">
@@ -1806,7 +1806,7 @@
         </is>
       </c>
       <c r="E12" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F12" s="6" t="n">
         <v>10</v>
@@ -1820,13 +1820,13 @@
         </is>
       </c>
       <c r="I12" s="4" t="n">
-        <v>59</v>
+        <v>29</v>
       </c>
       <c r="J12" s="4" t="n">
         <v>58</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>1</v>
+        <v>-29</v>
       </c>
       <c r="L12" s="4" t="inlineStr">
         <is>
@@ -1849,8 +1849,8 @@
       <c r="P12" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Q12" s="9" t="n">
-        <v>1</v>
+      <c r="Q12" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R12" s="9" t="n">
         <v>0</v>
@@ -1865,7 +1865,7 @@
         <v>0</v>
       </c>
       <c r="V12" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W12" s="9" t="n">
         <v>0</v>
@@ -1917,17 +1917,17 @@
         </is>
       </c>
       <c r="I13" s="4" t="n">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="J13" s="4" t="n">
         <v>29</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-12</v>
+      </c>
+      <c r="L13" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M13" s="8" t="n">
@@ -2111,13 +2111,13 @@
         </is>
       </c>
       <c r="I15" s="4" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="J15" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L15" s="4" t="inlineStr">
         <is>
@@ -2194,7 +2194,7 @@
         </is>
       </c>
       <c r="E16" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F16" s="6" t="n">
         <v>10</v>
@@ -2208,13 +2208,13 @@
         </is>
       </c>
       <c r="I16" s="4" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J16" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L16" s="4" t="inlineStr">
         <is>
@@ -2252,8 +2252,8 @@
       <c r="U16" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V16" s="9" t="n">
-        <v>0</v>
+      <c r="V16" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W16" s="9" t="n">
         <v>0</v>
@@ -2305,13 +2305,13 @@
         </is>
       </c>
       <c r="I17" s="4" t="n">
-        <v>64</v>
+        <v>40</v>
       </c>
       <c r="J17" s="4" t="n">
         <v>54</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>10</v>
+        <v>-14</v>
       </c>
       <c r="L17" s="4" t="inlineStr">
         <is>
@@ -2402,17 +2402,17 @@
         </is>
       </c>
       <c r="I18" s="4" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="J18" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-10</v>
+      </c>
+      <c r="L18" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M18" s="8" t="n">
@@ -2499,13 +2499,13 @@
         </is>
       </c>
       <c r="I19" s="4" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="J19" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>0</v>
+        <v>-9</v>
       </c>
       <c r="L19" s="7" t="inlineStr">
         <is>
@@ -2596,13 +2596,13 @@
         </is>
       </c>
       <c r="I20" s="4" t="n">
-        <v>45</v>
+        <v>27</v>
       </c>
       <c r="J20" s="4" t="n">
         <v>38</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>7</v>
+        <v>-11</v>
       </c>
       <c r="L20" s="4" t="inlineStr">
         <is>
@@ -2693,17 +2693,17 @@
         </is>
       </c>
       <c r="I21" s="4" t="n">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="J21" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-9</v>
+      </c>
+      <c r="L21" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M21" s="8" t="n">
@@ -2776,7 +2776,7 @@
         </is>
       </c>
       <c r="E22" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F22" s="6" t="n">
         <v>10</v>
@@ -2790,13 +2790,13 @@
         </is>
       </c>
       <c r="I22" s="4" t="n">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="J22" s="4" t="n">
         <v>39</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>7</v>
+        <v>-2</v>
       </c>
       <c r="L22" s="4" t="inlineStr">
         <is>
@@ -2837,8 +2837,8 @@
       <c r="V22" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W22" s="9" t="n">
-        <v>3</v>
+      <c r="W22" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="X22" s="10" t="n">
         <v>7</v>
@@ -2887,17 +2887,17 @@
         </is>
       </c>
       <c r="I23" s="4" t="n">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="J23" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>7</v>
-      </c>
-      <c r="L23" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-3</v>
+      </c>
+      <c r="L23" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M23" s="8" t="n">
@@ -2984,13 +2984,13 @@
         </is>
       </c>
       <c r="I24" s="4" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="J24" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="L24" s="7" t="inlineStr">
         <is>
@@ -3029,7 +3029,7 @@
         <v>0</v>
       </c>
       <c r="V24" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="W24" s="9" t="n">
         <v>0</v>
@@ -3081,13 +3081,13 @@
         </is>
       </c>
       <c r="I25" s="4" t="n">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="J25" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>2</v>
+        <v>-4</v>
       </c>
       <c r="L25" s="4" t="inlineStr">
         <is>
@@ -3126,7 +3126,7 @@
         <v>0</v>
       </c>
       <c r="V25" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W25" s="9" t="n">
         <v>0</v>
@@ -3164,7 +3164,7 @@
         </is>
       </c>
       <c r="E26" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F26" s="6" t="n">
         <v>10</v>
@@ -3178,13 +3178,13 @@
         </is>
       </c>
       <c r="I26" s="4" t="n">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="J26" s="4" t="n">
         <v>31</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="L26" s="4" t="inlineStr">
         <is>
@@ -3208,7 +3208,7 @@
         <v>0</v>
       </c>
       <c r="Q26" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R26" s="9" t="n">
         <v>0</v>
@@ -3225,8 +3225,8 @@
       <c r="V26" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W26" s="9" t="n">
-        <v>2</v>
+      <c r="W26" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="X26" s="10" t="n">
         <v>5</v>
@@ -3275,13 +3275,13 @@
         </is>
       </c>
       <c r="I27" s="4" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="J27" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L27" s="7" t="inlineStr">
         <is>
@@ -3320,7 +3320,7 @@
         <v>0</v>
       </c>
       <c r="V27" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="W27" s="9" t="n">
         <v>0</v>
@@ -3372,13 +3372,13 @@
         </is>
       </c>
       <c r="I28" s="4" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="J28" s="4" t="n">
         <v>23</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L28" s="4" t="inlineStr">
         <is>
@@ -3469,17 +3469,17 @@
         </is>
       </c>
       <c r="I29" s="4" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="J29" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L29" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-6</v>
+      </c>
+      <c r="L29" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M29" s="8" t="n">
@@ -3566,13 +3566,13 @@
         </is>
       </c>
       <c r="I30" s="4" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="J30" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="L30" s="7" t="inlineStr">
         <is>
@@ -3663,13 +3663,13 @@
         </is>
       </c>
       <c r="I31" s="4" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="J31" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="L31" s="4" t="inlineStr">
         <is>
@@ -3711,7 +3711,7 @@
         <v>4</v>
       </c>
       <c r="W31" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="X31" s="10" t="n">
         <v>6</v>
@@ -3760,13 +3760,13 @@
         </is>
       </c>
       <c r="I32" s="4" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J32" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L32" s="7" t="inlineStr">
         <is>
@@ -3808,7 +3808,7 @@
         <v>4</v>
       </c>
       <c r="W32" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="X32" s="9" t="n">
         <v>0</v>
@@ -3857,17 +3857,17 @@
         </is>
       </c>
       <c r="I33" s="4" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="J33" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L33" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-8</v>
+      </c>
+      <c r="L33" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M33" s="8" t="n">
@@ -4051,13 +4051,13 @@
         </is>
       </c>
       <c r="I35" s="4" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="J35" s="4" t="n">
         <v>30</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L35" s="4" t="inlineStr">
         <is>
@@ -4096,7 +4096,7 @@
         <v>0</v>
       </c>
       <c r="V35" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W35" s="9" t="n">
         <v>0</v>
@@ -4148,13 +4148,13 @@
         </is>
       </c>
       <c r="I36" s="4" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="J36" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K36" s="4" t="n">
-        <v>0</v>
+        <v>-8</v>
       </c>
       <c r="L36" s="7" t="inlineStr">
         <is>
@@ -4193,7 +4193,7 @@
         <v>0</v>
       </c>
       <c r="V36" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W36" s="9" t="n">
         <v>0</v>
@@ -4231,7 +4231,7 @@
         </is>
       </c>
       <c r="E37" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F37" s="6" t="n">
         <v>10</v>
@@ -4245,13 +4245,13 @@
         </is>
       </c>
       <c r="I37" s="4" t="n">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="J37" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K37" s="4" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="L37" s="4" t="inlineStr">
         <is>
@@ -4289,11 +4289,11 @@
       <c r="U37" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V37" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="W37" s="9" t="n">
-        <v>0</v>
+      <c r="V37" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="W37" s="10" t="n">
+        <v>13</v>
       </c>
       <c r="X37" s="9" t="n">
         <v>3</v>
@@ -4301,8 +4301,8 @@
       <c r="Y37" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z37" s="9" t="n">
-        <v>0</v>
+      <c r="Z37" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="AA37" s="10" t="n">
         <v>1</v>
@@ -4342,13 +4342,13 @@
         </is>
       </c>
       <c r="I38" s="4" t="n">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="J38" s="4" t="n">
         <v>36</v>
       </c>
       <c r="K38" s="4" t="n">
-        <v>6</v>
+        <v>-2</v>
       </c>
       <c r="L38" s="4" t="inlineStr">
         <is>
@@ -4439,17 +4439,17 @@
         </is>
       </c>
       <c r="I39" s="4" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="J39" s="4" t="n">
         <v>30</v>
       </c>
       <c r="K39" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L39" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-30</v>
+      </c>
+      <c r="L39" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M39" s="8" t="n">
@@ -4536,13 +4536,13 @@
         </is>
       </c>
       <c r="I40" s="4" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J40" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K40" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L40" s="7" t="inlineStr">
         <is>
@@ -4633,13 +4633,13 @@
         </is>
       </c>
       <c r="I41" s="4" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="J41" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K41" s="4" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="L41" s="7" t="inlineStr">
         <is>
@@ -4678,7 +4678,7 @@
         <v>0</v>
       </c>
       <c r="V41" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W41" s="9" t="n">
         <v>0</v>
@@ -4730,13 +4730,13 @@
         </is>
       </c>
       <c r="I42" s="4" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="J42" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K42" s="4" t="n">
-        <v>0</v>
+        <v>-8</v>
       </c>
       <c r="L42" s="7" t="inlineStr">
         <is>
@@ -4827,13 +4827,13 @@
         </is>
       </c>
       <c r="I43" s="4" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="J43" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K43" s="4" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="L43" s="7" t="inlineStr">
         <is>
@@ -4872,7 +4872,7 @@
         <v>0</v>
       </c>
       <c r="V43" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W43" s="9" t="n">
         <v>0</v>
@@ -4924,13 +4924,13 @@
         </is>
       </c>
       <c r="I44" s="4" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="J44" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K44" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L44" s="7" t="inlineStr">
         <is>
@@ -5007,7 +5007,7 @@
         </is>
       </c>
       <c r="E45" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F45" s="6" t="n">
         <v>10</v>
@@ -5021,13 +5021,13 @@
         </is>
       </c>
       <c r="I45" s="4" t="n">
-        <v>38</v>
+        <v>23</v>
       </c>
       <c r="J45" s="4" t="n">
         <v>31</v>
       </c>
       <c r="K45" s="4" t="n">
-        <v>7</v>
+        <v>-8</v>
       </c>
       <c r="L45" s="4" t="inlineStr">
         <is>
@@ -5048,7 +5048,7 @@
         </is>
       </c>
       <c r="P45" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q45" s="9" t="n">
         <v>1</v>
@@ -5068,8 +5068,8 @@
       <c r="V45" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W45" s="9" t="n">
-        <v>3</v>
+      <c r="W45" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="X45" s="10" t="n">
         <v>4</v>
@@ -5118,13 +5118,13 @@
         </is>
       </c>
       <c r="I46" s="4" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="J46" s="4" t="n">
         <v>40</v>
       </c>
       <c r="K46" s="4" t="n">
-        <v>-11</v>
+        <v>-15</v>
       </c>
       <c r="L46" s="4" t="inlineStr">
         <is>
@@ -5215,13 +5215,13 @@
         </is>
       </c>
       <c r="I47" s="4" t="n">
-        <v>36</v>
+        <v>21</v>
       </c>
       <c r="J47" s="4" t="n">
         <v>36</v>
       </c>
       <c r="K47" s="4" t="n">
-        <v>0</v>
+        <v>-15</v>
       </c>
       <c r="L47" s="4" t="inlineStr">
         <is>
@@ -5260,7 +5260,7 @@
         <v>0</v>
       </c>
       <c r="V47" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W47" s="9" t="n">
         <v>0</v>
@@ -5312,13 +5312,13 @@
         </is>
       </c>
       <c r="I48" s="4" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="J48" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K48" s="4" t="n">
-        <v>0</v>
+        <v>-12</v>
       </c>
       <c r="L48" s="7" t="inlineStr">
         <is>
@@ -5357,7 +5357,7 @@
         <v>0</v>
       </c>
       <c r="V48" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W48" s="9" t="n">
         <v>0</v>
@@ -5409,13 +5409,13 @@
         </is>
       </c>
       <c r="I49" s="4" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="J49" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K49" s="4" t="n">
-        <v>0</v>
+        <v>-6</v>
       </c>
       <c r="L49" s="4" t="inlineStr">
         <is>
@@ -5506,13 +5506,13 @@
         </is>
       </c>
       <c r="I50" s="4" t="n">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="J50" s="4" t="n">
         <v>29</v>
       </c>
       <c r="K50" s="4" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="L50" s="4" t="inlineStr">
         <is>
@@ -5551,7 +5551,7 @@
         <v>0</v>
       </c>
       <c r="V50" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W50" s="9" t="n">
         <v>0</v>
@@ -5603,13 +5603,13 @@
         </is>
       </c>
       <c r="I51" s="4" t="n">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="J51" s="4" t="n">
         <v>34</v>
       </c>
       <c r="K51" s="4" t="n">
-        <v>4</v>
+        <v>-5</v>
       </c>
       <c r="L51" s="4" t="inlineStr">
         <is>
@@ -5651,7 +5651,7 @@
         <v>4</v>
       </c>
       <c r="W51" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="X51" s="10" t="n">
         <v>5</v>
@@ -5700,17 +5700,17 @@
         </is>
       </c>
       <c r="I52" s="4" t="n">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="J52" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K52" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L52" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-9</v>
+      </c>
+      <c r="L52" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M52" s="8" t="n">
@@ -5797,13 +5797,13 @@
         </is>
       </c>
       <c r="I53" s="4" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="J53" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K53" s="4" t="n">
-        <v>2</v>
+        <v>-4</v>
       </c>
       <c r="L53" s="7" t="inlineStr">
         <is>
@@ -5842,7 +5842,7 @@
         <v>0</v>
       </c>
       <c r="V53" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W53" s="9" t="n">
         <v>0</v>
@@ -5894,13 +5894,13 @@
         </is>
       </c>
       <c r="I54" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J54" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K54" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L54" s="7" t="inlineStr">
         <is>
@@ -5991,17 +5991,17 @@
         </is>
       </c>
       <c r="I55" s="4" t="n">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="J55" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K55" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="L55" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-8</v>
+      </c>
+      <c r="L55" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M55" s="8" t="n">
@@ -6088,17 +6088,17 @@
         </is>
       </c>
       <c r="I56" s="4" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="J56" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K56" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L56" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-3</v>
+      </c>
+      <c r="L56" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M56" s="8" t="n">
@@ -6365,7 +6365,7 @@
         </is>
       </c>
       <c r="E59" s="5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F59" s="6" t="n">
         <v>10</v>
@@ -6379,13 +6379,13 @@
         </is>
       </c>
       <c r="I59" s="4" t="n">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="J59" s="4" t="n">
         <v>33</v>
       </c>
       <c r="K59" s="4" t="n">
-        <v>3</v>
+        <v>-2</v>
       </c>
       <c r="L59" s="4" t="inlineStr">
         <is>
@@ -6423,8 +6423,8 @@
       <c r="U59" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="V59" s="9" t="n">
-        <v>3</v>
+      <c r="V59" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W59" s="9" t="n">
         <v>0</v>
@@ -6476,13 +6476,13 @@
         </is>
       </c>
       <c r="I60" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J60" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K60" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L60" s="7" t="inlineStr">
         <is>
@@ -6521,7 +6521,7 @@
         <v>0</v>
       </c>
       <c r="V60" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W60" s="9" t="n">
         <v>0</v>
@@ -6573,13 +6573,13 @@
         </is>
       </c>
       <c r="I61" s="4" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="J61" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K61" s="4" t="n">
-        <v>0</v>
+        <v>-6</v>
       </c>
       <c r="L61" s="7" t="inlineStr">
         <is>
@@ -6670,13 +6670,13 @@
         </is>
       </c>
       <c r="I62" s="4" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="J62" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K62" s="4" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="L62" s="7" t="inlineStr">
         <is>
@@ -6767,13 +6767,13 @@
         </is>
       </c>
       <c r="I63" s="4" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="J63" s="4" t="n">
         <v>18</v>
       </c>
       <c r="K63" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L63" s="7" t="inlineStr">
         <is>
@@ -6864,13 +6864,13 @@
         </is>
       </c>
       <c r="I64" s="4" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="J64" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K64" s="4" t="n">
-        <v>2</v>
+        <v>-2</v>
       </c>
       <c r="L64" s="7" t="inlineStr">
         <is>
@@ -6891,7 +6891,7 @@
         </is>
       </c>
       <c r="P64" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q64" s="9" t="n">
         <v>0</v>
@@ -6961,13 +6961,13 @@
         </is>
       </c>
       <c r="I65" s="4" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="J65" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K65" s="4" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="L65" s="7" t="inlineStr">
         <is>
@@ -6991,7 +6991,7 @@
         <v>1</v>
       </c>
       <c r="Q65" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R65" s="9" t="n">
         <v>0</v>
@@ -7058,13 +7058,13 @@
         </is>
       </c>
       <c r="I66" s="4" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="J66" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K66" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L66" s="7" t="inlineStr">
         <is>
@@ -7155,13 +7155,13 @@
         </is>
       </c>
       <c r="I67" s="4" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="J67" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K67" s="4" t="n">
-        <v>2</v>
+        <v>-7</v>
       </c>
       <c r="L67" s="7" t="inlineStr">
         <is>
@@ -7200,7 +7200,7 @@
         <v>0</v>
       </c>
       <c r="V67" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W67" s="9" t="n">
         <v>0</v>
@@ -7252,13 +7252,13 @@
         </is>
       </c>
       <c r="I68" s="4" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="J68" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K68" s="4" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="L68" s="7" t="inlineStr">
         <is>
@@ -7297,7 +7297,7 @@
         <v>0</v>
       </c>
       <c r="V68" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W68" s="9" t="n">
         <v>0</v>
@@ -7349,17 +7349,17 @@
         </is>
       </c>
       <c r="I69" s="4" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="J69" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K69" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L69" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-3</v>
+      </c>
+      <c r="L69" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M69" s="8" t="n">
@@ -7394,7 +7394,7 @@
         <v>0</v>
       </c>
       <c r="V69" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W69" s="9" t="n">
         <v>0</v>
@@ -7432,7 +7432,7 @@
         </is>
       </c>
       <c r="E70" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F70" s="6" t="n">
         <v>10</v>
@@ -7446,13 +7446,13 @@
         </is>
       </c>
       <c r="I70" s="4" t="n">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="J70" s="4" t="n">
         <v>23</v>
       </c>
       <c r="K70" s="4" t="n">
-        <v>6</v>
+        <v>-3</v>
       </c>
       <c r="L70" s="4" t="inlineStr">
         <is>
@@ -7481,8 +7481,8 @@
       <c r="R70" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S70" s="9" t="n">
-        <v>1</v>
+      <c r="S70" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="T70" s="10" t="n">
         <v>1</v>
@@ -7494,7 +7494,7 @@
         <v>4</v>
       </c>
       <c r="W70" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X70" s="10" t="n">
         <v>7</v>
@@ -7543,13 +7543,13 @@
         </is>
       </c>
       <c r="I71" s="4" t="n">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="J71" s="4" t="n">
         <v>33</v>
       </c>
       <c r="K71" s="4" t="n">
-        <v>1</v>
+        <v>-7</v>
       </c>
       <c r="L71" s="4" t="inlineStr">
         <is>
@@ -7588,7 +7588,7 @@
         <v>0</v>
       </c>
       <c r="V71" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W71" s="9" t="n">
         <v>0</v>
@@ -7685,7 +7685,7 @@
         <v>0</v>
       </c>
       <c r="V72" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W72" s="9" t="n">
         <v>0</v>
@@ -7737,17 +7737,17 @@
         </is>
       </c>
       <c r="I73" s="4" t="n">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="J73" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K73" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L73" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-6</v>
+      </c>
+      <c r="L73" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M73" s="8" t="n">
@@ -7782,7 +7782,7 @@
         <v>0</v>
       </c>
       <c r="V73" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W73" s="9" t="n">
         <v>0</v>
@@ -7834,13 +7834,13 @@
         </is>
       </c>
       <c r="I74" s="4" t="n">
-        <v>37</v>
+        <v>22</v>
       </c>
       <c r="J74" s="4" t="n">
         <v>33</v>
       </c>
       <c r="K74" s="4" t="n">
-        <v>4</v>
+        <v>-11</v>
       </c>
       <c r="L74" s="4" t="inlineStr">
         <is>
@@ -7931,13 +7931,13 @@
         </is>
       </c>
       <c r="I75" s="4" t="n">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="J75" s="4" t="n">
         <v>29</v>
       </c>
       <c r="K75" s="4" t="n">
-        <v>4</v>
+        <v>-7</v>
       </c>
       <c r="L75" s="4" t="inlineStr">
         <is>
@@ -7979,7 +7979,7 @@
         <v>4</v>
       </c>
       <c r="W75" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X75" s="9" t="n">
         <v>2</v>
@@ -8028,17 +8028,17 @@
         </is>
       </c>
       <c r="I76" s="4" t="n">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="J76" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K76" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="L76" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-10</v>
+      </c>
+      <c r="L76" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M76" s="8" t="n">
@@ -8076,7 +8076,7 @@
         <v>4</v>
       </c>
       <c r="W76" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X76" s="9" t="n">
         <v>3</v>
@@ -8111,7 +8111,7 @@
         </is>
       </c>
       <c r="E77" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F77" s="6" t="n">
         <v>10</v>
@@ -8125,13 +8125,13 @@
         </is>
       </c>
       <c r="I77" s="4" t="n">
-        <v>45</v>
+        <v>23</v>
       </c>
       <c r="J77" s="4" t="n">
         <v>42</v>
       </c>
       <c r="K77" s="4" t="n">
-        <v>3</v>
+        <v>-19</v>
       </c>
       <c r="L77" s="4" t="inlineStr">
         <is>
@@ -8169,8 +8169,8 @@
       <c r="U77" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V77" s="9" t="n">
-        <v>3</v>
+      <c r="V77" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W77" s="9" t="n">
         <v>0</v>
@@ -8222,17 +8222,17 @@
         </is>
       </c>
       <c r="I78" s="4" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="J78" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K78" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L78" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-5</v>
+      </c>
+      <c r="L78" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M78" s="8" t="n">
@@ -8267,7 +8267,7 @@
         <v>0</v>
       </c>
       <c r="V78" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W78" s="9" t="n">
         <v>0</v>
@@ -8402,7 +8402,7 @@
         </is>
       </c>
       <c r="E80" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F80" s="6" t="n">
         <v>10</v>
@@ -8416,13 +8416,13 @@
         </is>
       </c>
       <c r="I80" s="4" t="n">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="J80" s="4" t="n">
         <v>29</v>
       </c>
       <c r="K80" s="4" t="n">
-        <v>7</v>
+        <v>-3</v>
       </c>
       <c r="L80" s="4" t="inlineStr">
         <is>
@@ -8443,10 +8443,10 @@
         </is>
       </c>
       <c r="P80" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q80" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R80" s="9" t="n">
         <v>0</v>
@@ -8463,8 +8463,8 @@
       <c r="V80" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W80" s="9" t="n">
-        <v>3</v>
+      <c r="W80" s="10" t="n">
+        <v>6</v>
       </c>
       <c r="X80" s="10" t="n">
         <v>5</v>
@@ -8513,17 +8513,17 @@
         </is>
       </c>
       <c r="I81" s="4" t="n">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="J81" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K81" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L81" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-8</v>
+      </c>
+      <c r="L81" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M81" s="8" t="n">
@@ -8558,7 +8558,7 @@
         <v>0</v>
       </c>
       <c r="V81" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W81" s="9" t="n">
         <v>0</v>
@@ -8610,13 +8610,13 @@
         </is>
       </c>
       <c r="I82" s="4" t="n">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="J82" s="4" t="n">
         <v>33</v>
       </c>
       <c r="K82" s="4" t="n">
-        <v>3</v>
+        <v>-7</v>
       </c>
       <c r="L82" s="4" t="inlineStr">
         <is>
@@ -8707,17 +8707,17 @@
         </is>
       </c>
       <c r="I83" s="4" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="J83" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K83" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="L83" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-1</v>
+      </c>
+      <c r="L83" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M83" s="8" t="n">
@@ -8755,7 +8755,7 @@
         <v>4</v>
       </c>
       <c r="W83" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X83" s="10" t="n">
         <v>7</v>
@@ -8804,13 +8804,13 @@
         </is>
       </c>
       <c r="I84" s="4" t="n">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="J84" s="4" t="n">
         <v>28</v>
       </c>
       <c r="K84" s="4" t="n">
-        <v>5</v>
+        <v>-5</v>
       </c>
       <c r="L84" s="4" t="inlineStr">
         <is>
@@ -8852,7 +8852,7 @@
         <v>4</v>
       </c>
       <c r="W84" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="X84" s="10" t="n">
         <v>7</v>
@@ -8901,17 +8901,17 @@
         </is>
       </c>
       <c r="I85" s="4" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="J85" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K85" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="L85" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-1</v>
+      </c>
+      <c r="L85" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M85" s="8" t="n">
@@ -8998,17 +8998,17 @@
         </is>
       </c>
       <c r="I86" s="4" t="n">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="J86" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K86" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="L86" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-6</v>
+      </c>
+      <c r="L86" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M86" s="8" t="n">
@@ -9081,7 +9081,7 @@
         </is>
       </c>
       <c r="E87" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F87" s="6" t="n">
         <v>10</v>
@@ -9095,13 +9095,13 @@
         </is>
       </c>
       <c r="I87" s="4" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="J87" s="4" t="n">
         <v>19</v>
       </c>
       <c r="K87" s="4" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L87" s="4" t="inlineStr">
         <is>
@@ -9139,11 +9139,11 @@
       <c r="U87" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V87" s="9" t="n">
-        <v>3</v>
+      <c r="V87" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W87" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X87" s="10" t="n">
         <v>4</v>
@@ -9192,13 +9192,13 @@
         </is>
       </c>
       <c r="I88" s="4" t="n">
-        <v>45</v>
+        <v>33</v>
       </c>
       <c r="J88" s="4" t="n">
         <v>40</v>
       </c>
       <c r="K88" s="4" t="n">
-        <v>5</v>
+        <v>-7</v>
       </c>
       <c r="L88" s="4" t="inlineStr">
         <is>
@@ -9240,7 +9240,7 @@
         <v>4</v>
       </c>
       <c r="W88" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X88" s="10" t="n">
         <v>7</v>
@@ -9289,17 +9289,17 @@
         </is>
       </c>
       <c r="I89" s="4" t="n">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="J89" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K89" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L89" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-8</v>
+      </c>
+      <c r="L89" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M89" s="8" t="n">
@@ -9334,7 +9334,7 @@
         <v>0</v>
       </c>
       <c r="V89" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W89" s="9" t="n">
         <v>0</v>
@@ -9386,17 +9386,17 @@
         </is>
       </c>
       <c r="I90" s="4" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="J90" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K90" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L90" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-1</v>
+      </c>
+      <c r="L90" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M90" s="8" t="n">
@@ -9483,13 +9483,13 @@
         </is>
       </c>
       <c r="I91" s="4" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="J91" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K91" s="4" t="n">
-        <v>0</v>
+        <v>-6</v>
       </c>
       <c r="L91" s="7" t="inlineStr">
         <is>
@@ -9580,13 +9580,13 @@
         </is>
       </c>
       <c r="I92" s="4" t="n">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="J92" s="4" t="n">
         <v>31</v>
       </c>
       <c r="K92" s="4" t="n">
-        <v>4</v>
+        <v>-2</v>
       </c>
       <c r="L92" s="4" t="inlineStr">
         <is>
@@ -9628,7 +9628,7 @@
         <v>4</v>
       </c>
       <c r="W92" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X92" s="10" t="n">
         <v>7</v>
@@ -9663,7 +9663,7 @@
         </is>
       </c>
       <c r="E93" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F93" s="6" t="n">
         <v>10</v>
@@ -9704,10 +9704,10 @@
         </is>
       </c>
       <c r="P93" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q93" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R93" s="9" t="n">
         <v>0</v>
@@ -9715,8 +9715,8 @@
       <c r="S93" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T93" s="9" t="n">
-        <v>0</v>
+      <c r="T93" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U93" s="9" t="n">
         <v>0</v>
@@ -9774,13 +9774,13 @@
         </is>
       </c>
       <c r="I94" s="4" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="J94" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K94" s="4" t="n">
-        <v>0</v>
+        <v>-12</v>
       </c>
       <c r="L94" s="7" t="inlineStr">
         <is>
@@ -9857,7 +9857,7 @@
         </is>
       </c>
       <c r="E95" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F95" s="6" t="n">
         <v>10</v>
@@ -9871,13 +9871,13 @@
         </is>
       </c>
       <c r="I95" s="4" t="n">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="J95" s="4" t="n">
         <v>32</v>
       </c>
       <c r="K95" s="4" t="n">
-        <v>3</v>
+        <v>-6</v>
       </c>
       <c r="L95" s="4" t="inlineStr">
         <is>
@@ -9915,11 +9915,11 @@
       <c r="U95" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V95" s="9" t="n">
-        <v>3</v>
+      <c r="V95" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W95" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X95" s="10" t="n">
         <v>4</v>
@@ -10065,13 +10065,13 @@
         </is>
       </c>
       <c r="I97" s="4" t="n">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="J97" s="4" t="n">
         <v>35</v>
       </c>
       <c r="K97" s="4" t="n">
-        <v>4</v>
+        <v>-3</v>
       </c>
       <c r="L97" s="4" t="inlineStr">
         <is>
@@ -10092,7 +10092,7 @@
         </is>
       </c>
       <c r="P97" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q97" s="9" t="n">
         <v>1</v>
@@ -10113,7 +10113,7 @@
         <v>4</v>
       </c>
       <c r="W97" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="X97" s="10" t="n">
         <v>6</v>
@@ -10162,17 +10162,17 @@
         </is>
       </c>
       <c r="I98" s="4" t="n">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="J98" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K98" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L98" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-13</v>
+      </c>
+      <c r="L98" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M98" s="8" t="n">
@@ -10259,13 +10259,13 @@
         </is>
       </c>
       <c r="I99" s="4" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="J99" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K99" s="4" t="n">
-        <v>1</v>
+        <v>-5</v>
       </c>
       <c r="L99" s="7" t="inlineStr">
         <is>
@@ -10304,7 +10304,7 @@
         <v>0</v>
       </c>
       <c r="V99" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W99" s="9" t="n">
         <v>0</v>
@@ -10356,17 +10356,17 @@
         </is>
       </c>
       <c r="I100" s="4" t="n">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="J100" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K100" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L100" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-14</v>
+      </c>
+      <c r="L100" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M100" s="8" t="n">
@@ -10401,7 +10401,7 @@
         <v>0</v>
       </c>
       <c r="V100" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W100" s="9" t="n">
         <v>0</v>
@@ -10439,7 +10439,7 @@
         </is>
       </c>
       <c r="E101" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F101" s="6" t="n">
         <v>10</v>
@@ -10453,13 +10453,13 @@
         </is>
       </c>
       <c r="I101" s="4" t="n">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="J101" s="4" t="n">
         <v>35</v>
       </c>
       <c r="K101" s="4" t="n">
-        <v>4</v>
+        <v>-1</v>
       </c>
       <c r="L101" s="4" t="inlineStr">
         <is>
@@ -10500,8 +10500,8 @@
       <c r="V101" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W101" s="9" t="n">
-        <v>0</v>
+      <c r="W101" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="X101" s="10" t="n">
         <v>4</v>
@@ -10550,17 +10550,17 @@
         </is>
       </c>
       <c r="I102" s="4" t="n">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="J102" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K102" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L102" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-8</v>
+      </c>
+      <c r="L102" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M102" s="8" t="n">
@@ -10647,17 +10647,17 @@
         </is>
       </c>
       <c r="I103" s="4" t="n">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="J103" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K103" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L103" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-9</v>
+      </c>
+      <c r="L103" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M103" s="8" t="n">
@@ -10744,13 +10744,13 @@
         </is>
       </c>
       <c r="I104" s="4" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="J104" s="4" t="n">
         <v>33</v>
       </c>
       <c r="K104" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L104" s="4" t="inlineStr">
         <is>
@@ -10789,7 +10789,7 @@
         <v>0</v>
       </c>
       <c r="V104" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W104" s="9" t="n">
         <v>0</v>
@@ -10827,7 +10827,7 @@
         </is>
       </c>
       <c r="E105" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F105" s="6" t="n">
         <v>10</v>
@@ -10841,13 +10841,13 @@
         </is>
       </c>
       <c r="I105" s="4" t="n">
-        <v>46</v>
+        <v>35</v>
       </c>
       <c r="J105" s="4" t="n">
         <v>41</v>
       </c>
       <c r="K105" s="4" t="n">
-        <v>5</v>
+        <v>-6</v>
       </c>
       <c r="L105" s="4" t="inlineStr">
         <is>
@@ -10879,8 +10879,8 @@
       <c r="S105" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T105" s="9" t="n">
-        <v>0</v>
+      <c r="T105" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U105" s="9" t="n">
         <v>0</v>
@@ -10889,7 +10889,7 @@
         <v>4</v>
       </c>
       <c r="W105" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X105" s="10" t="n">
         <v>7</v>
@@ -10938,17 +10938,17 @@
         </is>
       </c>
       <c r="I106" s="4" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="J106" s="4" t="n">
         <v>19</v>
       </c>
       <c r="K106" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L106" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-3</v>
+      </c>
+      <c r="L106" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M106" s="8" t="n">
@@ -10983,7 +10983,7 @@
         <v>0</v>
       </c>
       <c r="V106" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W106" s="9" t="n">
         <v>0</v>
@@ -11035,13 +11035,13 @@
         </is>
       </c>
       <c r="I107" s="4" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="J107" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K107" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L107" s="7" t="inlineStr">
         <is>
@@ -11132,13 +11132,13 @@
         </is>
       </c>
       <c r="I108" s="4" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="J108" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K108" s="4" t="n">
-        <v>0</v>
+        <v>-14</v>
       </c>
       <c r="L108" s="7" t="inlineStr">
         <is>
@@ -11229,13 +11229,13 @@
         </is>
       </c>
       <c r="I109" s="4" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="J109" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K109" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L109" s="7" t="inlineStr">
         <is>
@@ -11274,7 +11274,7 @@
         <v>0</v>
       </c>
       <c r="V109" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W109" s="9" t="n">
         <v>0</v>
@@ -11326,13 +11326,13 @@
         </is>
       </c>
       <c r="I110" s="4" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="J110" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K110" s="4" t="n">
-        <v>3</v>
+        <v>-2</v>
       </c>
       <c r="L110" s="7" t="inlineStr">
         <is>
@@ -11423,13 +11423,13 @@
         </is>
       </c>
       <c r="I111" s="4" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="J111" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K111" s="4" t="n">
-        <v>2</v>
+        <v>-3</v>
       </c>
       <c r="L111" s="7" t="inlineStr">
         <is>
@@ -11520,17 +11520,17 @@
         </is>
       </c>
       <c r="I112" s="4" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J112" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K112" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="L112" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>7</v>
+      </c>
+      <c r="L112" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M112" s="8" t="n">
@@ -11547,7 +11547,7 @@
         </is>
       </c>
       <c r="P112" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q112" s="9" t="n">
         <v>0</v>
@@ -11603,7 +11603,7 @@
         </is>
       </c>
       <c r="E113" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F113" s="6" t="n">
         <v>10</v>
@@ -11661,11 +11661,11 @@
       <c r="U113" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V113" s="9" t="n">
-        <v>1</v>
+      <c r="V113" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W113" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X113" s="10" t="n">
         <v>7</v>
@@ -11714,17 +11714,17 @@
         </is>
       </c>
       <c r="I114" s="4" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="J114" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K114" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="L114" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-4</v>
+      </c>
+      <c r="L114" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M114" s="8" t="n">
@@ -11811,17 +11811,17 @@
         </is>
       </c>
       <c r="I115" s="4" t="n">
-        <v>53</v>
+        <v>7</v>
       </c>
       <c r="J115" s="4" t="n">
         <v>51</v>
       </c>
       <c r="K115" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L115" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-44</v>
+      </c>
+      <c r="L115" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M115" s="8" t="n">
@@ -11856,7 +11856,7 @@
         <v>0</v>
       </c>
       <c r="V115" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W115" s="9" t="n">
         <v>0</v>
@@ -11908,17 +11908,17 @@
         </is>
       </c>
       <c r="I116" s="4" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="J116" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K116" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L116" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-5</v>
+      </c>
+      <c r="L116" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M116" s="8" t="n">
@@ -11953,7 +11953,7 @@
         <v>0</v>
       </c>
       <c r="V116" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W116" s="9" t="n">
         <v>0</v>
@@ -11991,7 +11991,7 @@
         </is>
       </c>
       <c r="E117" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F117" s="6" t="n">
         <v>10</v>
@@ -12005,17 +12005,17 @@
         </is>
       </c>
       <c r="I117" s="4" t="n">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="J117" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K117" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L117" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-8</v>
+      </c>
+      <c r="L117" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M117" s="8" t="n">
@@ -12049,8 +12049,8 @@
       <c r="U117" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V117" s="9" t="n">
-        <v>2</v>
+      <c r="V117" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W117" s="9" t="n">
         <v>0</v>
@@ -12102,17 +12102,17 @@
         </is>
       </c>
       <c r="I118" s="4" t="n">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="J118" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K118" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="L118" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-4</v>
+      </c>
+      <c r="L118" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M118" s="8" t="n">
@@ -12199,13 +12199,13 @@
         </is>
       </c>
       <c r="I119" s="4" t="n">
-        <v>39</v>
+        <v>21</v>
       </c>
       <c r="J119" s="4" t="n">
         <v>34</v>
       </c>
       <c r="K119" s="4" t="n">
-        <v>5</v>
+        <v>-13</v>
       </c>
       <c r="L119" s="4" t="inlineStr">
         <is>
@@ -12247,7 +12247,7 @@
         <v>4</v>
       </c>
       <c r="W119" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X119" s="10" t="n">
         <v>7</v>
@@ -12296,17 +12296,17 @@
         </is>
       </c>
       <c r="I120" s="4" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J120" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K120" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L120" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-20</v>
+      </c>
+      <c r="L120" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M120" s="8" t="n">
@@ -12393,13 +12393,13 @@
         </is>
       </c>
       <c r="I121" s="4" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="J121" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K121" s="4" t="n">
-        <v>0</v>
+        <v>-11</v>
       </c>
       <c r="L121" s="7" t="inlineStr">
         <is>
@@ -12490,13 +12490,13 @@
         </is>
       </c>
       <c r="I122" s="4" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="J122" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K122" s="4" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="L122" s="7" t="inlineStr">
         <is>
@@ -12573,7 +12573,7 @@
         </is>
       </c>
       <c r="E123" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F123" s="6" t="n">
         <v>10</v>
@@ -12587,13 +12587,13 @@
         </is>
       </c>
       <c r="I123" s="4" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="J123" s="4" t="n">
         <v>27</v>
       </c>
       <c r="K123" s="4" t="n">
-        <v>3</v>
+        <v>-1</v>
       </c>
       <c r="L123" s="4" t="inlineStr">
         <is>
@@ -12631,8 +12631,8 @@
       <c r="U123" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V123" s="9" t="n">
-        <v>3</v>
+      <c r="V123" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W123" s="9" t="n">
         <v>0</v>
@@ -12684,17 +12684,17 @@
         </is>
       </c>
       <c r="I124" s="4" t="n">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="J124" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K124" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L124" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-9</v>
+      </c>
+      <c r="L124" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M124" s="8" t="n">
@@ -12720,7 +12720,7 @@
         <v>1</v>
       </c>
       <c r="S124" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T124" s="10" t="n">
         <v>1</v>
@@ -12767,7 +12767,7 @@
         </is>
       </c>
       <c r="E125" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F125" s="6" t="n">
         <v>10</v>
@@ -12781,13 +12781,13 @@
         </is>
       </c>
       <c r="I125" s="4" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="J125" s="4" t="n">
         <v>41</v>
       </c>
       <c r="K125" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L125" s="4" t="inlineStr">
         <is>
@@ -12825,11 +12825,11 @@
       <c r="U125" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V125" s="9" t="n">
-        <v>0</v>
+      <c r="V125" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W125" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X125" s="10" t="n">
         <v>5</v>
@@ -12864,7 +12864,7 @@
         </is>
       </c>
       <c r="E126" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F126" s="6" t="n">
         <v>10</v>
@@ -12878,17 +12878,17 @@
         </is>
       </c>
       <c r="I126" s="4" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="J126" s="4" t="n">
         <v>18</v>
       </c>
       <c r="K126" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="L126" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-2</v>
+      </c>
+      <c r="L126" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M126" s="8" t="n">
@@ -12925,8 +12925,8 @@
       <c r="V126" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W126" s="9" t="n">
-        <v>2</v>
+      <c r="W126" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="X126" s="10" t="n">
         <v>4</v>
@@ -12975,13 +12975,13 @@
         </is>
       </c>
       <c r="I127" s="4" t="n">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="J127" s="4" t="n">
         <v>29</v>
       </c>
       <c r="K127" s="4" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="L127" s="4" t="inlineStr">
         <is>
@@ -13020,7 +13020,7 @@
         <v>0</v>
       </c>
       <c r="V127" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W127" s="9" t="n">
         <v>0</v>
@@ -13058,7 +13058,7 @@
         </is>
       </c>
       <c r="E128" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F128" s="6" t="n">
         <v>10</v>
@@ -13072,17 +13072,17 @@
         </is>
       </c>
       <c r="I128" s="4" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J128" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K128" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="L128" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>4</v>
+      </c>
+      <c r="L128" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M128" s="8" t="n">
@@ -13116,11 +13116,11 @@
       <c r="U128" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V128" s="9" t="n">
+      <c r="V128" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="W128" s="9" t="n">
         <v>2</v>
-      </c>
-      <c r="W128" s="9" t="n">
-        <v>0</v>
       </c>
       <c r="X128" s="10" t="n">
         <v>7</v>
@@ -13155,7 +13155,7 @@
         </is>
       </c>
       <c r="E129" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F129" s="6" t="n">
         <v>10</v>
@@ -13169,13 +13169,13 @@
         </is>
       </c>
       <c r="I129" s="4" t="n">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="J129" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K129" s="4" t="n">
-        <v>3</v>
+        <v>-6</v>
       </c>
       <c r="L129" s="7" t="inlineStr">
         <is>
@@ -13213,8 +13213,8 @@
       <c r="U129" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V129" s="9" t="n">
-        <v>3</v>
+      <c r="V129" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W129" s="9" t="n">
         <v>0</v>
@@ -13252,7 +13252,7 @@
         </is>
       </c>
       <c r="E130" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F130" s="6" t="n">
         <v>10</v>
@@ -13266,13 +13266,13 @@
         </is>
       </c>
       <c r="I130" s="4" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="J130" s="4" t="n">
         <v>18</v>
       </c>
       <c r="K130" s="4" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="L130" s="4" t="inlineStr">
         <is>
@@ -13313,8 +13313,8 @@
       <c r="V130" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W130" s="9" t="n">
-        <v>3</v>
+      <c r="W130" s="10" t="n">
+        <v>8</v>
       </c>
       <c r="X130" s="10" t="n">
         <v>4</v>
@@ -13363,13 +13363,13 @@
         </is>
       </c>
       <c r="I131" s="4" t="n">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="J131" s="4" t="n">
         <v>36</v>
       </c>
       <c r="K131" s="4" t="n">
-        <v>2</v>
+        <v>-8</v>
       </c>
       <c r="L131" s="4" t="inlineStr">
         <is>
@@ -13557,13 +13557,13 @@
         </is>
       </c>
       <c r="I133" s="4" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="J133" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K133" s="4" t="n">
-        <v>1</v>
+        <v>-7</v>
       </c>
       <c r="L133" s="7" t="inlineStr">
         <is>
@@ -13654,17 +13654,17 @@
         </is>
       </c>
       <c r="I134" s="4" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="J134" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K134" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L134" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-5</v>
+      </c>
+      <c r="L134" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M134" s="8" t="n">
@@ -13699,7 +13699,7 @@
         <v>0</v>
       </c>
       <c r="V134" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W134" s="9" t="n">
         <v>0</v>
@@ -13834,7 +13834,7 @@
         </is>
       </c>
       <c r="E136" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F136" s="6" t="n">
         <v>10</v>
@@ -13848,13 +13848,13 @@
         </is>
       </c>
       <c r="I136" s="4" t="n">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="J136" s="4" t="n">
         <v>31</v>
       </c>
       <c r="K136" s="4" t="n">
-        <v>4</v>
+        <v>-5</v>
       </c>
       <c r="L136" s="4" t="inlineStr">
         <is>
@@ -13895,8 +13895,8 @@
       <c r="V136" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W136" s="9" t="n">
-        <v>0</v>
+      <c r="W136" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="X136" s="10" t="n">
         <v>7</v>
@@ -13945,13 +13945,13 @@
         </is>
       </c>
       <c r="I137" s="4" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="J137" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K137" s="4" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="L137" s="7" t="inlineStr">
         <is>
@@ -14087,7 +14087,7 @@
         <v>0</v>
       </c>
       <c r="V138" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W138" s="9" t="n">
         <v>0</v>
@@ -14139,17 +14139,17 @@
         </is>
       </c>
       <c r="I139" s="4" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="J139" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K139" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L139" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-4</v>
+      </c>
+      <c r="L139" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M139" s="8" t="n">
@@ -14169,7 +14169,7 @@
         <v>1</v>
       </c>
       <c r="Q139" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R139" s="9" t="n">
         <v>0</v>
@@ -14184,7 +14184,7 @@
         <v>0</v>
       </c>
       <c r="V139" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W139" s="9" t="n">
         <v>0</v>
@@ -14236,17 +14236,17 @@
         </is>
       </c>
       <c r="I140" s="4" t="n">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="J140" s="4" t="n">
         <v>24</v>
       </c>
       <c r="K140" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="L140" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-8</v>
+      </c>
+      <c r="L140" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M140" s="8" t="n">
@@ -14333,13 +14333,13 @@
         </is>
       </c>
       <c r="I141" s="4" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="J141" s="4" t="n">
         <v>18</v>
       </c>
       <c r="K141" s="4" t="n">
-        <v>1</v>
+        <v>-5</v>
       </c>
       <c r="L141" s="7" t="inlineStr">
         <is>
@@ -14430,13 +14430,13 @@
         </is>
       </c>
       <c r="I142" s="4" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J142" s="4" t="n">
         <v>18</v>
       </c>
       <c r="K142" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L142" s="4" t="inlineStr">
         <is>
@@ -14527,13 +14527,13 @@
         </is>
       </c>
       <c r="I143" s="4" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="J143" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K143" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L143" s="7" t="inlineStr">
         <is>
@@ -14572,7 +14572,7 @@
         <v>0</v>
       </c>
       <c r="V143" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W143" s="9" t="n">
         <v>0</v>
@@ -14624,13 +14624,13 @@
         </is>
       </c>
       <c r="I144" s="4" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="J144" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K144" s="4" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L144" s="7" t="inlineStr">
         <is>
@@ -14672,7 +14672,7 @@
         <v>4</v>
       </c>
       <c r="W144" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X144" s="10" t="n">
         <v>6</v>
@@ -14766,7 +14766,7 @@
         <v>0</v>
       </c>
       <c r="V145" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W145" s="9" t="n">
         <v>0</v>
@@ -14818,17 +14818,17 @@
         </is>
       </c>
       <c r="I146" s="4" t="n">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="J146" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K146" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="L146" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-6</v>
+      </c>
+      <c r="L146" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M146" s="8" t="n">
@@ -14915,13 +14915,13 @@
         </is>
       </c>
       <c r="I147" s="4" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="J147" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K147" s="4" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="L147" s="7" t="inlineStr">
         <is>
@@ -15012,13 +15012,13 @@
         </is>
       </c>
       <c r="I148" s="4" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="J148" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K148" s="4" t="n">
-        <v>2</v>
+        <v>-2</v>
       </c>
       <c r="L148" s="4" t="inlineStr">
         <is>
@@ -15057,7 +15057,7 @@
         <v>0</v>
       </c>
       <c r="V148" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W148" s="9" t="n">
         <v>0</v>
@@ -15109,13 +15109,13 @@
         </is>
       </c>
       <c r="I149" s="4" t="n">
-        <v>53</v>
+        <v>27</v>
       </c>
       <c r="J149" s="4" t="n">
         <v>40</v>
       </c>
       <c r="K149" s="4" t="n">
-        <v>13</v>
+        <v>-13</v>
       </c>
       <c r="L149" s="4" t="inlineStr">
         <is>
@@ -15157,7 +15157,7 @@
         <v>4</v>
       </c>
       <c r="W149" s="10" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X149" s="10" t="n">
         <v>7</v>
@@ -15206,17 +15206,17 @@
         </is>
       </c>
       <c r="I150" s="4" t="n">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="J150" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K150" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="L150" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-6</v>
+      </c>
+      <c r="L150" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M150" s="8" t="n">
@@ -15254,7 +15254,7 @@
         <v>4</v>
       </c>
       <c r="W150" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="X150" s="10" t="n">
         <v>7</v>
@@ -15303,13 +15303,13 @@
         </is>
       </c>
       <c r="I151" s="4" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="J151" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K151" s="4" t="n">
-        <v>0</v>
+        <v>-6</v>
       </c>
       <c r="L151" s="7" t="inlineStr">
         <is>
@@ -15330,10 +15330,10 @@
         </is>
       </c>
       <c r="P151" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q151" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R151" s="9" t="n">
         <v>0</v>
@@ -15400,17 +15400,17 @@
         </is>
       </c>
       <c r="I152" s="4" t="n">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="J152" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K152" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="L152" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-8</v>
+      </c>
+      <c r="L152" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M152" s="8" t="n">
@@ -15497,17 +15497,17 @@
         </is>
       </c>
       <c r="I153" s="4" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="J153" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K153" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L153" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-3</v>
+      </c>
+      <c r="L153" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M153" s="8" t="n">
@@ -15594,17 +15594,17 @@
         </is>
       </c>
       <c r="I154" s="4" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="J154" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K154" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L154" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-5</v>
+      </c>
+      <c r="L154" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M154" s="8" t="n">
@@ -15639,7 +15639,7 @@
         <v>0</v>
       </c>
       <c r="V154" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W154" s="9" t="n">
         <v>0</v>
@@ -15691,13 +15691,13 @@
         </is>
       </c>
       <c r="I155" s="4" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="J155" s="4" t="n">
         <v>29</v>
       </c>
       <c r="K155" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L155" s="4" t="inlineStr">
         <is>
@@ -15736,7 +15736,7 @@
         <v>0</v>
       </c>
       <c r="V155" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W155" s="9" t="n">
         <v>0</v>
@@ -15788,17 +15788,17 @@
         </is>
       </c>
       <c r="I156" s="4" t="n">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="J156" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K156" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L156" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-15</v>
+      </c>
+      <c r="L156" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M156" s="8" t="n">
@@ -15939,7 +15939,7 @@
         <v>6</v>
       </c>
       <c r="D2" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -15972,7 +15972,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="E3" t="n">
         <v>1</v>
@@ -15987,7 +15987,7 @@
         <v>1</v>
       </c>
       <c r="I3" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -16005,7 +16005,7 @@
         <v>6</v>
       </c>
       <c r="D4" t="n">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -16020,7 +16020,7 @@
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5">
@@ -16038,7 +16038,7 @@
         <v>6</v>
       </c>
       <c r="D5" t="n">
-        <v>1.67</v>
+        <v>1.83</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -16053,7 +16053,7 @@
         <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -16071,7 +16071,7 @@
         <v>6</v>
       </c>
       <c r="D6" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -16086,7 +16086,7 @@
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7">
@@ -16119,7 +16119,7 @@
         <v>1</v>
       </c>
       <c r="I7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8">
@@ -16137,7 +16137,7 @@
         <v>6</v>
       </c>
       <c r="D8" t="n">
-        <v>0.83</v>
+        <v>1.33</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -16152,7 +16152,7 @@
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
@@ -16170,7 +16170,7 @@
         <v>5</v>
       </c>
       <c r="D9" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -16251,7 +16251,7 @@
         <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -16269,7 +16269,7 @@
         <v>6</v>
       </c>
       <c r="D12" t="n">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="E12" t="n">
         <v>1</v>
@@ -16335,7 +16335,7 @@
         <v>6</v>
       </c>
       <c r="D14" t="n">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -16350,7 +16350,7 @@
         <v>1</v>
       </c>
       <c r="I14" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="15">
@@ -16368,7 +16368,7 @@
         <v>4</v>
       </c>
       <c r="D15" t="n">
-        <v>1.5</v>
+        <v>1.75</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -16383,7 +16383,7 @@
         <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16">
@@ -16401,7 +16401,7 @@
         <v>5</v>
       </c>
       <c r="D16" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -16416,7 +16416,7 @@
         <v>1</v>
       </c>
       <c r="I16" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17">
@@ -16434,7 +16434,7 @@
         <v>6</v>
       </c>
       <c r="D17" t="n">
-        <v>1.67</v>
+        <v>1.83</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -16449,7 +16449,7 @@
         <v>0</v>
       </c>
       <c r="I17" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="18">
@@ -16467,7 +16467,7 @@
         <v>6</v>
       </c>
       <c r="D18" t="n">
-        <v>0.83</v>
+        <v>1.17</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -16482,7 +16482,7 @@
         <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="19">
@@ -16500,7 +16500,7 @@
         <v>6</v>
       </c>
       <c r="D19" t="n">
-        <v>2</v>
+        <v>2.17</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
@@ -16515,7 +16515,7 @@
         <v>0</v>
       </c>
       <c r="I19" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20">
@@ -16533,22 +16533,22 @@
         <v>5</v>
       </c>
       <c r="D20" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="E20" t="n">
+        <v>1</v>
+      </c>
+      <c r="F20" t="n">
+        <v>4</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" t="n">
         <v>2</v>
-      </c>
-      <c r="E20" t="n">
-        <v>0</v>
-      </c>
-      <c r="F20" t="n">
-        <v>5</v>
-      </c>
-      <c r="G20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I20" t="n">
-        <v>5</v>
       </c>
     </row>
     <row r="21">
@@ -16599,7 +16599,7 @@
         <v>4</v>
       </c>
       <c r="D22" t="n">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
@@ -16614,7 +16614,7 @@
         <v>0</v>
       </c>
       <c r="I22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23">
@@ -16632,7 +16632,7 @@
         <v>4</v>
       </c>
       <c r="D23" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
@@ -16647,7 +16647,7 @@
         <v>0</v>
       </c>
       <c r="I23" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -16665,7 +16665,7 @@
         <v>5</v>
       </c>
       <c r="D24" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
@@ -16680,7 +16680,7 @@
         <v>0</v>
       </c>
       <c r="I24" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25">
@@ -16698,7 +16698,7 @@
         <v>5</v>
       </c>
       <c r="D25" t="n">
-        <v>1.6</v>
+        <v>2.4</v>
       </c>
       <c r="E25" t="n">
         <v>0</v>
@@ -16713,7 +16713,7 @@
         <v>0</v>
       </c>
       <c r="I25" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="26">
@@ -16731,7 +16731,7 @@
         <v>5</v>
       </c>
       <c r="D26" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="E26" t="n">
         <v>0</v>
@@ -16746,7 +16746,7 @@
         <v>1</v>
       </c>
       <c r="I26" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="27">
@@ -16764,7 +16764,7 @@
         <v>6</v>
       </c>
       <c r="D27" t="n">
-        <v>1.67</v>
+        <v>1.83</v>
       </c>
       <c r="E27" t="n">
         <v>0</v>
@@ -16779,7 +16779,7 @@
         <v>0</v>
       </c>
       <c r="I27" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="28">
@@ -16812,7 +16812,7 @@
         <v>0</v>
       </c>
       <c r="I28" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="29">
@@ -16845,7 +16845,7 @@
         <v>1</v>
       </c>
       <c r="I29" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="30">
@@ -16878,7 +16878,7 @@
         <v>0</v>
       </c>
       <c r="I30" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/docs/d/231/inyear.xlsx
+++ b/docs/d/231/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 08:33 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 08:39 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/231/inyear.xlsx
+++ b/docs/d/231/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 08:39 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 10:56 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/231/inyear.xlsx
+++ b/docs/d/231/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 10:56 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 11:03 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/231/inyear.xlsx
+++ b/docs/d/231/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 11:03 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 13:06 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/231/inyear.xlsx
+++ b/docs/d/231/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 13:06 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 17-Oct-2026. Built 2026-10-18 11:32 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>262 days remain until 30 June 2027, when these scores become final.</t>
+          <t>255 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (81 days) - 7 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (74 days) - 7 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (140 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (133 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (171 days) - 27 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (164 days) - 27 clubs short</t>
         </is>
       </c>
     </row>
@@ -947,13 +947,13 @@
         </is>
       </c>
       <c r="I3" s="4" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="J3" s="4" t="n">
         <v>35</v>
       </c>
       <c r="K3" s="4" t="n">
-        <v>-13</v>
+        <v>-11</v>
       </c>
       <c r="L3" s="4" t="inlineStr">
         <is>
@@ -977,7 +977,7 @@
         <v>0</v>
       </c>
       <c r="Q3" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R3" s="9" t="n">
         <v>0</v>
@@ -995,7 +995,7 @@
         <v>4</v>
       </c>
       <c r="W3" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X3" s="10" t="n">
         <v>6</v>
@@ -1044,13 +1044,13 @@
         </is>
       </c>
       <c r="I4" s="4" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J4" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K4" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L4" s="4" t="inlineStr">
         <is>
@@ -1092,7 +1092,7 @@
         <v>4</v>
       </c>
       <c r="W4" s="10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="X4" s="10" t="n">
         <v>6</v>
@@ -1820,13 +1820,13 @@
         </is>
       </c>
       <c r="I12" s="4" t="n">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="J12" s="4" t="n">
         <v>58</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>-29</v>
+        <v>-23</v>
       </c>
       <c r="L12" s="4" t="inlineStr">
         <is>
@@ -1865,7 +1865,7 @@
         <v>0</v>
       </c>
       <c r="V12" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W12" s="9" t="n">
         <v>0</v>
@@ -2097,7 +2097,7 @@
         </is>
       </c>
       <c r="E15" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F15" s="6" t="n">
         <v>10</v>
@@ -2111,13 +2111,13 @@
         </is>
       </c>
       <c r="I15" s="4" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="J15" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L15" s="4" t="inlineStr">
         <is>
@@ -2155,8 +2155,8 @@
       <c r="U15" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="V15" s="9" t="n">
-        <v>2</v>
+      <c r="V15" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W15" s="9" t="n">
         <v>0</v>
@@ -2429,10 +2429,10 @@
         </is>
       </c>
       <c r="P18" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q18" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R18" s="9" t="n">
         <v>0</v>
@@ -2776,7 +2776,7 @@
         </is>
       </c>
       <c r="E22" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F22" s="6" t="n">
         <v>10</v>
@@ -2816,8 +2816,8 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P22" s="9" t="n">
-        <v>3</v>
+      <c r="P22" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Q22" s="9" t="n">
         <v>1</v>
@@ -3178,13 +3178,13 @@
         </is>
       </c>
       <c r="I26" s="4" t="n">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="J26" s="4" t="n">
         <v>31</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="L26" s="4" t="inlineStr">
         <is>
@@ -3226,7 +3226,7 @@
         <v>4</v>
       </c>
       <c r="W26" s="10" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="X26" s="10" t="n">
         <v>5</v>
@@ -3402,7 +3402,7 @@
         <v>0</v>
       </c>
       <c r="Q28" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R28" s="9" t="n">
         <v>0</v>
@@ -3649,7 +3649,7 @@
         </is>
       </c>
       <c r="E31" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F31" s="6" t="n">
         <v>10</v>
@@ -3701,8 +3701,8 @@
       <c r="S31" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T31" s="9" t="n">
-        <v>0</v>
+      <c r="T31" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U31" s="9" t="n">
         <v>0</v>
@@ -4328,7 +4328,7 @@
         </is>
       </c>
       <c r="E38" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F38" s="6" t="n">
         <v>10</v>
@@ -4342,13 +4342,13 @@
         </is>
       </c>
       <c r="I38" s="4" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="J38" s="4" t="n">
         <v>36</v>
       </c>
       <c r="K38" s="4" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="L38" s="4" t="inlineStr">
         <is>
@@ -4371,8 +4371,8 @@
       <c r="P38" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="Q38" s="9" t="n">
-        <v>1</v>
+      <c r="Q38" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R38" s="9" t="n">
         <v>0</v>
@@ -4390,7 +4390,7 @@
         <v>4</v>
       </c>
       <c r="W38" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="X38" s="10" t="n">
         <v>6</v>
@@ -5007,7 +5007,7 @@
         </is>
       </c>
       <c r="E45" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F45" s="6" t="n">
         <v>10</v>
@@ -5050,8 +5050,8 @@
       <c r="P45" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="Q45" s="9" t="n">
-        <v>1</v>
+      <c r="Q45" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R45" s="9" t="n">
         <v>0</v>
@@ -5783,7 +5783,7 @@
         </is>
       </c>
       <c r="E53" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F53" s="6" t="n">
         <v>10</v>
@@ -5797,13 +5797,13 @@
         </is>
       </c>
       <c r="I53" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J53" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K53" s="4" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="L53" s="7" t="inlineStr">
         <is>
@@ -5841,8 +5841,8 @@
       <c r="U53" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V53" s="9" t="n">
-        <v>3</v>
+      <c r="V53" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W53" s="9" t="n">
         <v>0</v>
@@ -6670,13 +6670,13 @@
         </is>
       </c>
       <c r="I62" s="4" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="J62" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K62" s="4" t="n">
-        <v>-4</v>
+        <v>-2</v>
       </c>
       <c r="L62" s="7" t="inlineStr">
         <is>
@@ -6697,13 +6697,13 @@
         </is>
       </c>
       <c r="P62" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q62" s="10" t="n">
         <v>2</v>
       </c>
       <c r="R62" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S62" s="9" t="n">
         <v>1</v>
@@ -6715,7 +6715,7 @@
         <v>0</v>
       </c>
       <c r="V62" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W62" s="9" t="n">
         <v>0</v>
@@ -6864,13 +6864,13 @@
         </is>
       </c>
       <c r="I64" s="4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J64" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K64" s="4" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="L64" s="7" t="inlineStr">
         <is>
@@ -7141,7 +7141,7 @@
         </is>
       </c>
       <c r="E67" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F67" s="6" t="n">
         <v>10</v>
@@ -7193,8 +7193,8 @@
       <c r="S67" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T67" s="9" t="n">
-        <v>0</v>
+      <c r="T67" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U67" s="9" t="n">
         <v>0</v>
@@ -7349,13 +7349,13 @@
         </is>
       </c>
       <c r="I69" s="4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J69" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K69" s="4" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="L69" s="7" t="inlineStr">
         <is>
@@ -7394,7 +7394,7 @@
         <v>0</v>
       </c>
       <c r="V69" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W69" s="9" t="n">
         <v>0</v>
@@ -7640,13 +7640,13 @@
         </is>
       </c>
       <c r="I72" s="4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J72" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K72" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L72" s="7" t="inlineStr">
         <is>
@@ -7685,7 +7685,7 @@
         <v>0</v>
       </c>
       <c r="V72" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W72" s="9" t="n">
         <v>0</v>
@@ -8125,13 +8125,13 @@
         </is>
       </c>
       <c r="I77" s="4" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J77" s="4" t="n">
         <v>42</v>
       </c>
       <c r="K77" s="4" t="n">
-        <v>-19</v>
+        <v>-18</v>
       </c>
       <c r="L77" s="4" t="inlineStr">
         <is>
@@ -8222,13 +8222,13 @@
         </is>
       </c>
       <c r="I78" s="4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J78" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K78" s="4" t="n">
-        <v>-5</v>
+        <v>-4</v>
       </c>
       <c r="L78" s="7" t="inlineStr">
         <is>
@@ -8402,7 +8402,7 @@
         </is>
       </c>
       <c r="E80" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F80" s="6" t="n">
         <v>10</v>
@@ -8416,13 +8416,13 @@
         </is>
       </c>
       <c r="I80" s="4" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="J80" s="4" t="n">
         <v>29</v>
       </c>
       <c r="K80" s="4" t="n">
-        <v>-3</v>
+        <v>0</v>
       </c>
       <c r="L80" s="4" t="inlineStr">
         <is>
@@ -8445,8 +8445,8 @@
       <c r="P80" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="Q80" s="9" t="n">
-        <v>1</v>
+      <c r="Q80" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R80" s="9" t="n">
         <v>0</v>
@@ -8984,7 +8984,7 @@
         </is>
       </c>
       <c r="E86" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F86" s="6" t="n">
         <v>10</v>
@@ -8998,13 +8998,13 @@
         </is>
       </c>
       <c r="I86" s="4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J86" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K86" s="4" t="n">
-        <v>-6</v>
+        <v>-5</v>
       </c>
       <c r="L86" s="7" t="inlineStr">
         <is>
@@ -9042,8 +9042,8 @@
       <c r="U86" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V86" s="9" t="n">
-        <v>3</v>
+      <c r="V86" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W86" s="9" t="n">
         <v>0</v>
@@ -9095,13 +9095,13 @@
         </is>
       </c>
       <c r="I87" s="4" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="J87" s="4" t="n">
         <v>19</v>
       </c>
       <c r="K87" s="4" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="L87" s="4" t="inlineStr">
         <is>
@@ -9143,7 +9143,7 @@
         <v>4</v>
       </c>
       <c r="W87" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="X87" s="10" t="n">
         <v>4</v>
@@ -10051,7 +10051,7 @@
         </is>
       </c>
       <c r="E97" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F97" s="6" t="n">
         <v>10</v>
@@ -10065,13 +10065,13 @@
         </is>
       </c>
       <c r="I97" s="4" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="J97" s="4" t="n">
         <v>35</v>
       </c>
       <c r="K97" s="4" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="L97" s="4" t="inlineStr">
         <is>
@@ -10112,8 +10112,8 @@
       <c r="V97" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W97" s="9" t="n">
-        <v>3</v>
+      <c r="W97" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="X97" s="10" t="n">
         <v>6</v>
@@ -10162,13 +10162,13 @@
         </is>
       </c>
       <c r="I98" s="4" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="J98" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K98" s="4" t="n">
-        <v>-13</v>
+        <v>-11</v>
       </c>
       <c r="L98" s="7" t="inlineStr">
         <is>
@@ -10356,13 +10356,13 @@
         </is>
       </c>
       <c r="I100" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J100" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K100" s="4" t="n">
-        <v>-14</v>
+        <v>-13</v>
       </c>
       <c r="L100" s="7" t="inlineStr">
         <is>
@@ -10453,13 +10453,13 @@
         </is>
       </c>
       <c r="I101" s="4" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="J101" s="4" t="n">
         <v>35</v>
       </c>
       <c r="K101" s="4" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="L101" s="4" t="inlineStr">
         <is>
@@ -10647,13 +10647,13 @@
         </is>
       </c>
       <c r="I103" s="4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J103" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K103" s="4" t="n">
-        <v>-9</v>
+        <v>-8</v>
       </c>
       <c r="L103" s="7" t="inlineStr">
         <is>
@@ -10874,7 +10874,7 @@
         <v>2</v>
       </c>
       <c r="R105" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S105" s="9" t="n">
         <v>0</v>
@@ -11062,7 +11062,7 @@
         </is>
       </c>
       <c r="P107" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q107" s="9" t="n">
         <v>0</v>
@@ -11229,13 +11229,13 @@
         </is>
       </c>
       <c r="I109" s="4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J109" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K109" s="4" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="L109" s="7" t="inlineStr">
         <is>
@@ -11423,13 +11423,13 @@
         </is>
       </c>
       <c r="I111" s="4" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="J111" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K111" s="4" t="n">
-        <v>-3</v>
+        <v>-1</v>
       </c>
       <c r="L111" s="7" t="inlineStr">
         <is>
@@ -11714,13 +11714,13 @@
         </is>
       </c>
       <c r="I114" s="4" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="J114" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K114" s="4" t="n">
-        <v>-4</v>
+        <v>-1</v>
       </c>
       <c r="L114" s="7" t="inlineStr">
         <is>
@@ -11762,7 +11762,7 @@
         <v>4</v>
       </c>
       <c r="W114" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X114" s="10" t="n">
         <v>7</v>
@@ -11908,13 +11908,13 @@
         </is>
       </c>
       <c r="I116" s="4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J116" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K116" s="4" t="n">
-        <v>-5</v>
+        <v>-4</v>
       </c>
       <c r="L116" s="7" t="inlineStr">
         <is>
@@ -11953,7 +11953,7 @@
         <v>0</v>
       </c>
       <c r="V116" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W116" s="9" t="n">
         <v>0</v>
@@ -12005,13 +12005,13 @@
         </is>
       </c>
       <c r="I117" s="4" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="J117" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K117" s="4" t="n">
-        <v>-8</v>
+        <v>-6</v>
       </c>
       <c r="L117" s="7" t="inlineStr">
         <is>
@@ -12199,13 +12199,13 @@
         </is>
       </c>
       <c r="I119" s="4" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J119" s="4" t="n">
         <v>34</v>
       </c>
       <c r="K119" s="4" t="n">
-        <v>-13</v>
+        <v>-12</v>
       </c>
       <c r="L119" s="4" t="inlineStr">
         <is>
@@ -12247,7 +12247,7 @@
         <v>4</v>
       </c>
       <c r="W119" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="X119" s="10" t="n">
         <v>7</v>
@@ -12490,13 +12490,13 @@
         </is>
       </c>
       <c r="I122" s="4" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J122" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K122" s="4" t="n">
-        <v>-4</v>
+        <v>-2</v>
       </c>
       <c r="L122" s="7" t="inlineStr">
         <is>
@@ -12535,7 +12535,7 @@
         <v>0</v>
       </c>
       <c r="V122" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W122" s="9" t="n">
         <v>0</v>
@@ -12670,7 +12670,7 @@
         </is>
       </c>
       <c r="E124" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F124" s="6" t="n">
         <v>10</v>
@@ -12684,13 +12684,13 @@
         </is>
       </c>
       <c r="I124" s="4" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="J124" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K124" s="4" t="n">
-        <v>-9</v>
+        <v>-7</v>
       </c>
       <c r="L124" s="7" t="inlineStr">
         <is>
@@ -12728,8 +12728,8 @@
       <c r="U124" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="V124" s="9" t="n">
-        <v>2</v>
+      <c r="V124" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W124" s="9" t="n">
         <v>0</v>
@@ -12878,13 +12878,13 @@
         </is>
       </c>
       <c r="I126" s="4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J126" s="4" t="n">
         <v>18</v>
       </c>
       <c r="K126" s="4" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="L126" s="7" t="inlineStr">
         <is>
@@ -12926,7 +12926,7 @@
         <v>4</v>
       </c>
       <c r="W126" s="10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="X126" s="10" t="n">
         <v>4</v>
@@ -13834,7 +13834,7 @@
         </is>
       </c>
       <c r="E136" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F136" s="6" t="n">
         <v>10</v>
@@ -13848,13 +13848,13 @@
         </is>
       </c>
       <c r="I136" s="4" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="J136" s="4" t="n">
         <v>31</v>
       </c>
       <c r="K136" s="4" t="n">
-        <v>-5</v>
+        <v>-3</v>
       </c>
       <c r="L136" s="4" t="inlineStr">
         <is>
@@ -13886,8 +13886,8 @@
       <c r="S136" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="T136" s="9" t="n">
-        <v>0</v>
+      <c r="T136" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U136" s="9" t="n">
         <v>0</v>
@@ -13896,7 +13896,7 @@
         <v>4</v>
       </c>
       <c r="W136" s="10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="X136" s="10" t="n">
         <v>7</v>
@@ -14028,7 +14028,7 @@
         </is>
       </c>
       <c r="E138" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F138" s="6" t="n">
         <v>10</v>
@@ -14042,13 +14042,13 @@
         </is>
       </c>
       <c r="I138" s="4" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="J138" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K138" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L138" s="4" t="inlineStr">
         <is>
@@ -14086,8 +14086,8 @@
       <c r="U138" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V138" s="9" t="n">
-        <v>3</v>
+      <c r="V138" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W138" s="9" t="n">
         <v>0</v>
@@ -14139,17 +14139,17 @@
         </is>
       </c>
       <c r="I139" s="4" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="J139" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K139" s="4" t="n">
-        <v>-4</v>
-      </c>
-      <c r="L139" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>-2</v>
+      </c>
+      <c r="L139" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M139" s="8" t="n">
@@ -14236,13 +14236,13 @@
         </is>
       </c>
       <c r="I140" s="4" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="J140" s="4" t="n">
         <v>24</v>
       </c>
       <c r="K140" s="4" t="n">
-        <v>-8</v>
+        <v>-6</v>
       </c>
       <c r="L140" s="7" t="inlineStr">
         <is>
@@ -14527,13 +14527,13 @@
         </is>
       </c>
       <c r="I143" s="4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J143" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K143" s="4" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="L143" s="7" t="inlineStr">
         <is>
@@ -14624,13 +14624,13 @@
         </is>
       </c>
       <c r="I144" s="4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J144" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K144" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L144" s="7" t="inlineStr">
         <is>
@@ -15109,13 +15109,13 @@
         </is>
       </c>
       <c r="I149" s="4" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="J149" s="4" t="n">
         <v>40</v>
       </c>
       <c r="K149" s="4" t="n">
-        <v>-13</v>
+        <v>-10</v>
       </c>
       <c r="L149" s="4" t="inlineStr">
         <is>
@@ -15157,7 +15157,7 @@
         <v>4</v>
       </c>
       <c r="W149" s="10" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X149" s="10" t="n">
         <v>7</v>
@@ -15192,7 +15192,7 @@
         </is>
       </c>
       <c r="E150" s="5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F150" s="6" t="n">
         <v>10</v>
@@ -15206,13 +15206,13 @@
         </is>
       </c>
       <c r="I150" s="4" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="J150" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K150" s="4" t="n">
-        <v>-6</v>
+        <v>-4</v>
       </c>
       <c r="L150" s="7" t="inlineStr">
         <is>
@@ -15233,10 +15233,10 @@
         </is>
       </c>
       <c r="P150" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q150" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="Q150" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R150" s="9" t="n">
         <v>0</v>
@@ -15253,8 +15253,8 @@
       <c r="V150" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W150" s="9" t="n">
-        <v>3</v>
+      <c r="W150" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="X150" s="10" t="n">
         <v>7</v>
@@ -15386,7 +15386,7 @@
         </is>
       </c>
       <c r="E152" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F152" s="6" t="n">
         <v>10</v>
@@ -15400,13 +15400,13 @@
         </is>
       </c>
       <c r="I152" s="4" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="J152" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K152" s="4" t="n">
-        <v>-8</v>
+        <v>-6</v>
       </c>
       <c r="L152" s="7" t="inlineStr">
         <is>
@@ -15444,8 +15444,8 @@
       <c r="U152" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V152" s="9" t="n">
-        <v>3</v>
+      <c r="V152" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W152" s="9" t="n">
         <v>0</v>
@@ -15691,13 +15691,13 @@
         </is>
       </c>
       <c r="I155" s="4" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J155" s="4" t="n">
         <v>29</v>
       </c>
       <c r="K155" s="4" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="L155" s="4" t="inlineStr">
         <is>
@@ -15788,13 +15788,13 @@
         </is>
       </c>
       <c r="I156" s="4" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="J156" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K156" s="4" t="n">
-        <v>-15</v>
+        <v>-12</v>
       </c>
       <c r="L156" s="7" t="inlineStr">
         <is>
@@ -16005,7 +16005,7 @@
         <v>6</v>
       </c>
       <c r="D4" t="n">
-        <v>2</v>
+        <v>2.17</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -16038,7 +16038,7 @@
         <v>6</v>
       </c>
       <c r="D5" t="n">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -16104,7 +16104,7 @@
         <v>5</v>
       </c>
       <c r="D7" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -16137,7 +16137,7 @@
         <v>6</v>
       </c>
       <c r="D8" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -16170,7 +16170,7 @@
         <v>5</v>
       </c>
       <c r="D9" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -16236,7 +16236,7 @@
         <v>6</v>
       </c>
       <c r="D11" t="n">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -16302,7 +16302,7 @@
         <v>5</v>
       </c>
       <c r="D13" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -16401,7 +16401,7 @@
         <v>5</v>
       </c>
       <c r="D16" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -16434,7 +16434,7 @@
         <v>6</v>
       </c>
       <c r="D17" t="n">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -16500,13 +16500,13 @@
         <v>6</v>
       </c>
       <c r="D19" t="n">
-        <v>2.17</v>
+        <v>2.33</v>
       </c>
       <c r="E19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F19" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
@@ -16665,13 +16665,13 @@
         <v>5</v>
       </c>
       <c r="D24" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="E24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F24" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
@@ -16764,7 +16764,7 @@
         <v>6</v>
       </c>
       <c r="D27" t="n">
-        <v>1.83</v>
+        <v>2.17</v>
       </c>
       <c r="E27" t="n">
         <v>0</v>
@@ -16779,7 +16779,7 @@
         <v>0</v>
       </c>
       <c r="I27" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="28">
@@ -16830,13 +16830,13 @@
         <v>5</v>
       </c>
       <c r="D29" t="n">
-        <v>1.6</v>
+        <v>2</v>
       </c>
       <c r="E29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F29" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
@@ -16863,7 +16863,7 @@
         <v>5</v>
       </c>
       <c r="D30" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="E30" t="n">
         <v>0</v>

--- a/docs/d/231/inyear.xlsx
+++ b/docs/d/231/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 17-Oct-2026. Built 2026-10-18 11:32 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 24-Oct-2026. Built 2026-10-25 11:50 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>255 days remain until 30 June 2027, when these scores become final.</t>
+          <t>248 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (74 days) - 7 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (67 days) - 7 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (133 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (126 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (164 days) - 27 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (157 days) - 27 clubs short</t>
         </is>
       </c>
     </row>
@@ -947,13 +947,13 @@
         </is>
       </c>
       <c r="I3" s="4" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J3" s="4" t="n">
         <v>35</v>
       </c>
       <c r="K3" s="4" t="n">
-        <v>-11</v>
+        <v>-10</v>
       </c>
       <c r="L3" s="4" t="inlineStr">
         <is>
@@ -995,7 +995,7 @@
         <v>4</v>
       </c>
       <c r="W3" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="X3" s="10" t="n">
         <v>6</v>
@@ -1047,10 +1047,10 @@
         <v>28</v>
       </c>
       <c r="J4" s="4" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="K4" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L4" s="4" t="inlineStr">
         <is>
@@ -1238,13 +1238,13 @@
         </is>
       </c>
       <c r="I6" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J6" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="L6" s="7" t="inlineStr">
         <is>
@@ -1726,10 +1726,10 @@
         <v>19</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L11" s="7" t="inlineStr">
         <is>
@@ -2873,7 +2873,7 @@
         </is>
       </c>
       <c r="E23" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F23" s="6" t="n">
         <v>10</v>
@@ -2925,8 +2925,8 @@
       <c r="S23" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T23" s="9" t="n">
-        <v>0</v>
+      <c r="T23" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U23" s="9" t="n">
         <v>0</v>
@@ -3178,13 +3178,13 @@
         </is>
       </c>
       <c r="I26" s="4" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="J26" s="4" t="n">
         <v>31</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="L26" s="4" t="inlineStr">
         <is>
@@ -3226,7 +3226,7 @@
         <v>4</v>
       </c>
       <c r="W26" s="10" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="X26" s="10" t="n">
         <v>5</v>
@@ -3305,7 +3305,7 @@
         <v>1</v>
       </c>
       <c r="Q27" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R27" s="9" t="n">
         <v>0</v>
@@ -3469,13 +3469,13 @@
         </is>
       </c>
       <c r="I29" s="4" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="J29" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>-6</v>
+        <v>-3</v>
       </c>
       <c r="L29" s="7" t="inlineStr">
         <is>
@@ -3514,7 +3514,7 @@
         <v>0</v>
       </c>
       <c r="V29" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W29" s="9" t="n">
         <v>0</v>
@@ -4536,13 +4536,13 @@
         </is>
       </c>
       <c r="I40" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J40" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K40" s="4" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="L40" s="7" t="inlineStr">
         <is>
@@ -4581,7 +4581,7 @@
         <v>0</v>
       </c>
       <c r="V40" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W40" s="9" t="n">
         <v>0</v>
@@ -4924,13 +4924,13 @@
         </is>
       </c>
       <c r="I44" s="4" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="J44" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K44" s="4" t="n">
-        <v>-3</v>
+        <v>-1</v>
       </c>
       <c r="L44" s="7" t="inlineStr">
         <is>
@@ -4969,7 +4969,7 @@
         <v>0</v>
       </c>
       <c r="V44" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W44" s="9" t="n">
         <v>0</v>
@@ -5054,7 +5054,7 @@
         <v>2</v>
       </c>
       <c r="R45" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S45" s="9" t="n">
         <v>1</v>
@@ -5506,13 +5506,13 @@
         </is>
       </c>
       <c r="I50" s="4" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J50" s="4" t="n">
         <v>29</v>
       </c>
       <c r="K50" s="4" t="n">
-        <v>-5</v>
+        <v>-4</v>
       </c>
       <c r="L50" s="4" t="inlineStr">
         <is>
@@ -5542,7 +5542,7 @@
         <v>0</v>
       </c>
       <c r="S50" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T50" s="9" t="n">
         <v>0</v>
@@ -5551,7 +5551,7 @@
         <v>0</v>
       </c>
       <c r="V50" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W50" s="9" t="n">
         <v>0</v>
@@ -5589,7 +5589,7 @@
         </is>
       </c>
       <c r="E51" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F51" s="6" t="n">
         <v>10</v>
@@ -5603,13 +5603,13 @@
         </is>
       </c>
       <c r="I51" s="4" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="J51" s="4" t="n">
         <v>34</v>
       </c>
       <c r="K51" s="4" t="n">
-        <v>-5</v>
+        <v>-4</v>
       </c>
       <c r="L51" s="4" t="inlineStr">
         <is>
@@ -5650,8 +5650,8 @@
       <c r="V51" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W51" s="9" t="n">
-        <v>3</v>
+      <c r="W51" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="X51" s="10" t="n">
         <v>5</v>
@@ -5797,13 +5797,13 @@
         </is>
       </c>
       <c r="I53" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J53" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K53" s="4" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="L53" s="7" t="inlineStr">
         <is>
@@ -5845,7 +5845,7 @@
         <v>4</v>
       </c>
       <c r="W53" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X53" s="9" t="n">
         <v>3</v>
@@ -6379,13 +6379,13 @@
         </is>
       </c>
       <c r="I59" s="4" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="J59" s="4" t="n">
         <v>33</v>
       </c>
       <c r="K59" s="4" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="L59" s="4" t="inlineStr">
         <is>
@@ -6427,7 +6427,7 @@
         <v>4</v>
       </c>
       <c r="W59" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X59" s="10" t="n">
         <v>7</v>
@@ -6573,13 +6573,13 @@
         </is>
       </c>
       <c r="I61" s="4" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J61" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K61" s="4" t="n">
-        <v>-6</v>
+        <v>-4</v>
       </c>
       <c r="L61" s="7" t="inlineStr">
         <is>
@@ -6618,7 +6618,7 @@
         <v>0</v>
       </c>
       <c r="V61" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W61" s="9" t="n">
         <v>0</v>
@@ -7449,10 +7449,10 @@
         <v>20</v>
       </c>
       <c r="J70" s="4" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K70" s="4" t="n">
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="L70" s="4" t="inlineStr">
         <is>
@@ -7931,13 +7931,13 @@
         </is>
       </c>
       <c r="I75" s="4" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J75" s="4" t="n">
         <v>29</v>
       </c>
       <c r="K75" s="4" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="L75" s="4" t="inlineStr">
         <is>
@@ -8028,13 +8028,13 @@
         </is>
       </c>
       <c r="I76" s="4" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="J76" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K76" s="4" t="n">
-        <v>-10</v>
+        <v>-8</v>
       </c>
       <c r="L76" s="7" t="inlineStr">
         <is>
@@ -8707,13 +8707,13 @@
         </is>
       </c>
       <c r="I83" s="4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J83" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K83" s="4" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="L83" s="7" t="inlineStr">
         <is>
@@ -8755,7 +8755,7 @@
         <v>4</v>
       </c>
       <c r="W83" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="X83" s="10" t="n">
         <v>7</v>
@@ -8901,13 +8901,13 @@
         </is>
       </c>
       <c r="I85" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J85" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K85" s="4" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="L85" s="7" t="inlineStr">
         <is>
@@ -8998,13 +8998,13 @@
         </is>
       </c>
       <c r="I86" s="4" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="J86" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K86" s="4" t="n">
-        <v>-5</v>
+        <v>-3</v>
       </c>
       <c r="L86" s="7" t="inlineStr">
         <is>
@@ -9178,7 +9178,7 @@
         </is>
       </c>
       <c r="E88" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F88" s="6" t="n">
         <v>10</v>
@@ -9192,13 +9192,13 @@
         </is>
       </c>
       <c r="I88" s="4" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="J88" s="4" t="n">
         <v>40</v>
       </c>
       <c r="K88" s="4" t="n">
-        <v>-7</v>
+        <v>-5</v>
       </c>
       <c r="L88" s="4" t="inlineStr">
         <is>
@@ -9239,8 +9239,8 @@
       <c r="V88" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W88" s="9" t="n">
-        <v>2</v>
+      <c r="W88" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="X88" s="10" t="n">
         <v>7</v>
@@ -9289,17 +9289,17 @@
         </is>
       </c>
       <c r="I89" s="4" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="J89" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K89" s="4" t="n">
-        <v>-8</v>
-      </c>
-      <c r="L89" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>-4</v>
+      </c>
+      <c r="L89" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M89" s="8" t="n">
@@ -10162,13 +10162,13 @@
         </is>
       </c>
       <c r="I98" s="4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J98" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K98" s="4" t="n">
-        <v>-11</v>
+        <v>-10</v>
       </c>
       <c r="L98" s="7" t="inlineStr">
         <is>
@@ -10207,7 +10207,7 @@
         <v>3</v>
       </c>
       <c r="V98" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W98" s="9" t="n">
         <v>0</v>
@@ -10342,7 +10342,7 @@
         </is>
       </c>
       <c r="E100" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F100" s="6" t="n">
         <v>10</v>
@@ -10356,13 +10356,13 @@
         </is>
       </c>
       <c r="I100" s="4" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="J100" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K100" s="4" t="n">
-        <v>-13</v>
+        <v>-11</v>
       </c>
       <c r="L100" s="7" t="inlineStr">
         <is>
@@ -10400,8 +10400,8 @@
       <c r="U100" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V100" s="9" t="n">
-        <v>3</v>
+      <c r="V100" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W100" s="9" t="n">
         <v>0</v>
@@ -10453,13 +10453,13 @@
         </is>
       </c>
       <c r="I101" s="4" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J101" s="4" t="n">
         <v>35</v>
       </c>
       <c r="K101" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L101" s="4" t="inlineStr">
         <is>
@@ -10480,10 +10480,10 @@
         </is>
       </c>
       <c r="P101" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q101" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R101" s="9" t="n">
         <v>0</v>
@@ -10501,7 +10501,7 @@
         <v>4</v>
       </c>
       <c r="W101" s="10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X101" s="10" t="n">
         <v>4</v>
@@ -10577,7 +10577,7 @@
         </is>
       </c>
       <c r="P102" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q102" s="9" t="n">
         <v>1</v>
@@ -10780,7 +10780,7 @@
         <v>0</v>
       </c>
       <c r="S104" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T104" s="9" t="n">
         <v>0</v>
@@ -10924,7 +10924,7 @@
         </is>
       </c>
       <c r="E106" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F106" s="6" t="n">
         <v>10</v>
@@ -10938,13 +10938,13 @@
         </is>
       </c>
       <c r="I106" s="4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J106" s="4" t="n">
         <v>19</v>
       </c>
       <c r="K106" s="4" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="L106" s="7" t="inlineStr">
         <is>
@@ -10982,8 +10982,8 @@
       <c r="U106" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V106" s="9" t="n">
-        <v>3</v>
+      <c r="V106" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W106" s="9" t="n">
         <v>0</v>
@@ -11312,7 +11312,7 @@
         </is>
       </c>
       <c r="E110" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F110" s="6" t="n">
         <v>10</v>
@@ -11326,13 +11326,13 @@
         </is>
       </c>
       <c r="I110" s="4" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J110" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K110" s="4" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="L110" s="7" t="inlineStr">
         <is>
@@ -11370,8 +11370,8 @@
       <c r="U110" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V110" s="9" t="n">
-        <v>3</v>
+      <c r="V110" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W110" s="9" t="n">
         <v>0</v>
@@ -11409,7 +11409,7 @@
         </is>
       </c>
       <c r="E111" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F111" s="6" t="n">
         <v>10</v>
@@ -11423,13 +11423,13 @@
         </is>
       </c>
       <c r="I111" s="4" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="J111" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K111" s="4" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="L111" s="7" t="inlineStr">
         <is>
@@ -11467,8 +11467,8 @@
       <c r="U111" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V111" s="9" t="n">
-        <v>2</v>
+      <c r="V111" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W111" s="9" t="n">
         <v>0</v>
@@ -11811,13 +11811,13 @@
         </is>
       </c>
       <c r="I115" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J115" s="4" t="n">
         <v>51</v>
       </c>
       <c r="K115" s="4" t="n">
-        <v>-44</v>
+        <v>-43</v>
       </c>
       <c r="L115" s="7" t="inlineStr">
         <is>
@@ -11894,7 +11894,7 @@
         </is>
       </c>
       <c r="E116" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F116" s="6" t="n">
         <v>10</v>
@@ -11908,13 +11908,13 @@
         </is>
       </c>
       <c r="I116" s="4" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J116" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K116" s="4" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="L116" s="7" t="inlineStr">
         <is>
@@ -11952,8 +11952,8 @@
       <c r="U116" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V116" s="9" t="n">
-        <v>3</v>
+      <c r="V116" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W116" s="9" t="n">
         <v>0</v>
@@ -12199,13 +12199,13 @@
         </is>
       </c>
       <c r="I119" s="4" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J119" s="4" t="n">
         <v>34</v>
       </c>
       <c r="K119" s="4" t="n">
-        <v>-12</v>
+        <v>-11</v>
       </c>
       <c r="L119" s="4" t="inlineStr">
         <is>
@@ -12573,7 +12573,7 @@
         </is>
       </c>
       <c r="E123" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F123" s="6" t="n">
         <v>10</v>
@@ -12616,11 +12616,11 @@
       <c r="P123" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="Q123" s="9" t="n">
-        <v>1</v>
+      <c r="Q123" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R123" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S123" s="10" t="n">
         <v>2</v>
@@ -12684,17 +12684,17 @@
         </is>
       </c>
       <c r="I124" s="4" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="J124" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K124" s="4" t="n">
-        <v>-7</v>
-      </c>
-      <c r="L124" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>-5</v>
+      </c>
+      <c r="L124" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M124" s="8" t="n">
@@ -12732,7 +12732,7 @@
         <v>4</v>
       </c>
       <c r="W124" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X124" s="10" t="n">
         <v>7</v>
@@ -12864,7 +12864,7 @@
         </is>
       </c>
       <c r="E126" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F126" s="6" t="n">
         <v>10</v>
@@ -12878,13 +12878,13 @@
         </is>
       </c>
       <c r="I126" s="4" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J126" s="4" t="n">
         <v>18</v>
       </c>
       <c r="K126" s="4" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="L126" s="7" t="inlineStr">
         <is>
@@ -12907,8 +12907,8 @@
       <c r="P126" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="Q126" s="9" t="n">
-        <v>1</v>
+      <c r="Q126" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R126" s="9" t="n">
         <v>0</v>
@@ -12961,7 +12961,7 @@
         </is>
       </c>
       <c r="E127" s="5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F127" s="6" t="n">
         <v>10</v>
@@ -12975,13 +12975,13 @@
         </is>
       </c>
       <c r="I127" s="4" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="J127" s="4" t="n">
         <v>29</v>
       </c>
       <c r="K127" s="4" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="L127" s="4" t="inlineStr">
         <is>
@@ -13002,7 +13002,7 @@
         </is>
       </c>
       <c r="P127" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q127" s="10" t="n">
         <v>2</v>
@@ -13010,8 +13010,8 @@
       <c r="R127" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S127" s="9" t="n">
-        <v>0</v>
+      <c r="S127" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="T127" s="10" t="n">
         <v>1</v>
@@ -13019,8 +13019,8 @@
       <c r="U127" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V127" s="9" t="n">
-        <v>3</v>
+      <c r="V127" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W127" s="9" t="n">
         <v>0</v>
@@ -13058,7 +13058,7 @@
         </is>
       </c>
       <c r="E128" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F128" s="6" t="n">
         <v>10</v>
@@ -13075,10 +13075,10 @@
         <v>18</v>
       </c>
       <c r="J128" s="4" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="K128" s="4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L128" s="7" t="inlineStr">
         <is>
@@ -13107,8 +13107,8 @@
       <c r="R128" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S128" s="9" t="n">
-        <v>1</v>
+      <c r="S128" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="T128" s="9" t="n">
         <v>0</v>
@@ -13729,15 +13729,15 @@
         </is>
       </c>
       <c r="C135" s="4" t="n">
-        <v>2584277</v>
+        <v>2817706</v>
       </c>
       <c r="D135" s="4" t="inlineStr">
         <is>
-          <t>Office Depot SSC Toastmasters</t>
+          <t>Oradea Toastmasters</t>
         </is>
       </c>
       <c r="E135" s="5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F135" s="6" t="n">
         <v>10</v>
@@ -13751,17 +13751,17 @@
         </is>
       </c>
       <c r="I135" s="4" t="n">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="J135" s="4" t="n">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="K135" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L135" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>-3</v>
+      </c>
+      <c r="L135" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M135" s="8" t="n">
@@ -13787,22 +13787,22 @@
         <v>0</v>
       </c>
       <c r="S135" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T135" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="T135" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U135" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V135" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="W135" s="9" t="n">
-        <v>0</v>
+      <c r="V135" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="W135" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="X135" s="10" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="Y135" s="9" t="n">
         <v>0</v>
@@ -13826,15 +13826,15 @@
         </is>
       </c>
       <c r="C136" s="4" t="n">
-        <v>2817706</v>
+        <v>7652775</v>
       </c>
       <c r="D136" s="4" t="inlineStr">
         <is>
-          <t>Oradea Toastmasters</t>
+          <t>Timisoara English Speakers</t>
         </is>
       </c>
       <c r="E136" s="5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F136" s="6" t="n">
         <v>10</v>
@@ -13848,17 +13848,17 @@
         </is>
       </c>
       <c r="I136" s="4" t="n">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="J136" s="4" t="n">
-        <v>31</v>
+        <v>12</v>
       </c>
       <c r="K136" s="4" t="n">
-        <v>-3</v>
-      </c>
-      <c r="L136" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>0</v>
+      </c>
+      <c r="L136" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M136" s="8" t="n">
@@ -13884,7 +13884,7 @@
         <v>0</v>
       </c>
       <c r="S136" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T136" s="10" t="n">
         <v>1</v>
@@ -13892,11 +13892,11 @@
       <c r="U136" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V136" s="10" t="n">
-        <v>4</v>
-      </c>
-      <c r="W136" s="10" t="n">
-        <v>5</v>
+      <c r="V136" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="W136" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="X136" s="10" t="n">
         <v>7</v>
@@ -13923,15 +13923,15 @@
         </is>
       </c>
       <c r="C137" s="4" t="n">
-        <v>7652775</v>
+        <v>1269633</v>
       </c>
       <c r="D137" s="4" t="inlineStr">
         <is>
-          <t>Timisoara English Speakers</t>
+          <t>Timisoara Toastmasters Club</t>
         </is>
       </c>
       <c r="E137" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F137" s="6" t="n">
         <v>10</v>
@@ -13945,17 +13945,17 @@
         </is>
       </c>
       <c r="I137" s="4" t="n">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="J137" s="4" t="n">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="K137" s="4" t="n">
-        <v>-1</v>
-      </c>
-      <c r="L137" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>3</v>
+      </c>
+      <c r="L137" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M137" s="8" t="n">
@@ -13972,7 +13972,7 @@
         </is>
       </c>
       <c r="P137" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q137" s="9" t="n">
         <v>0</v>
@@ -13989,8 +13989,8 @@
       <c r="U137" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V137" s="9" t="n">
-        <v>1</v>
+      <c r="V137" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W137" s="9" t="n">
         <v>0</v>
@@ -14020,15 +14020,15 @@
         </is>
       </c>
       <c r="C138" s="4" t="n">
-        <v>1269633</v>
+        <v>3760924</v>
       </c>
       <c r="D138" s="4" t="inlineStr">
         <is>
-          <t>Timisoara Toastmasters Club</t>
+          <t>Toastmasters Arad</t>
         </is>
       </c>
       <c r="E138" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F138" s="6" t="n">
         <v>10</v>
@@ -14042,13 +14042,13 @@
         </is>
       </c>
       <c r="I138" s="4" t="n">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="J138" s="4" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="K138" s="4" t="n">
-        <v>3</v>
+        <v>-2</v>
       </c>
       <c r="L138" s="4" t="inlineStr">
         <is>
@@ -14069,10 +14069,10 @@
         </is>
       </c>
       <c r="P138" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q138" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R138" s="9" t="n">
         <v>0</v>
@@ -14080,20 +14080,20 @@
       <c r="S138" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T138" s="10" t="n">
-        <v>1</v>
+      <c r="T138" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="U138" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V138" s="10" t="n">
-        <v>4</v>
+      <c r="V138" s="9" t="n">
+        <v>1</v>
       </c>
       <c r="W138" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X138" s="10" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Y138" s="9" t="n">
         <v>0</v>
@@ -14117,15 +14117,15 @@
         </is>
       </c>
       <c r="C139" s="4" t="n">
-        <v>3760924</v>
+        <v>1467750</v>
       </c>
       <c r="D139" s="4" t="inlineStr">
         <is>
-          <t>Toastmasters Arad</t>
+          <t>Toastmasters Cluj</t>
         </is>
       </c>
       <c r="E139" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F139" s="6" t="n">
         <v>10</v>
@@ -14139,17 +14139,17 @@
         </is>
       </c>
       <c r="I139" s="4" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J139" s="4" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="K139" s="4" t="n">
-        <v>-2</v>
-      </c>
-      <c r="L139" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-5</v>
+      </c>
+      <c r="L139" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M139" s="8" t="n">
@@ -14169,28 +14169,28 @@
         <v>1</v>
       </c>
       <c r="Q139" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R139" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S139" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T139" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="T139" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U139" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V139" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="W139" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X139" s="10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y139" s="9" t="n">
         <v>0</v>
@@ -14214,15 +14214,15 @@
         </is>
       </c>
       <c r="C140" s="4" t="n">
-        <v>1467750</v>
+        <v>2584277</v>
       </c>
       <c r="D140" s="4" t="inlineStr">
         <is>
-          <t>Toastmasters Cluj</t>
+          <t>Viking Office SSC Toastmasters</t>
         </is>
       </c>
       <c r="E140" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F140" s="6" t="n">
         <v>10</v>
@@ -14236,13 +14236,13 @@
         </is>
       </c>
       <c r="I140" s="4" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="J140" s="4" t="n">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="K140" s="4" t="n">
-        <v>-6</v>
+        <v>0</v>
       </c>
       <c r="L140" s="7" t="inlineStr">
         <is>
@@ -14263,7 +14263,7 @@
         </is>
       </c>
       <c r="P140" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q140" s="9" t="n">
         <v>0</v>
@@ -14272,22 +14272,22 @@
         <v>0</v>
       </c>
       <c r="S140" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="T140" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="T140" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="U140" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V140" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="W140" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X140" s="10" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="Y140" s="9" t="n">
         <v>0</v>
@@ -14527,13 +14527,13 @@
         </is>
       </c>
       <c r="I143" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J143" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K143" s="4" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="L143" s="7" t="inlineStr">
         <is>
@@ -14572,7 +14572,7 @@
         <v>0</v>
       </c>
       <c r="V143" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W143" s="9" t="n">
         <v>0</v>
@@ -14624,13 +14624,13 @@
         </is>
       </c>
       <c r="I144" s="4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J144" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K144" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L144" s="7" t="inlineStr">
         <is>
@@ -14672,7 +14672,7 @@
         <v>4</v>
       </c>
       <c r="W144" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="X144" s="10" t="n">
         <v>6</v>
@@ -15109,10 +15109,10 @@
         </is>
       </c>
       <c r="I149" s="4" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="J149" s="4" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="K149" s="4" t="n">
         <v>-10</v>
@@ -15206,13 +15206,13 @@
         </is>
       </c>
       <c r="I150" s="4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J150" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K150" s="4" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="L150" s="7" t="inlineStr">
         <is>
@@ -15239,7 +15239,7 @@
         <v>2</v>
       </c>
       <c r="R150" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S150" s="10" t="n">
         <v>2</v>
@@ -15303,13 +15303,13 @@
         </is>
       </c>
       <c r="I151" s="4" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J151" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K151" s="4" t="n">
-        <v>-6</v>
+        <v>-4</v>
       </c>
       <c r="L151" s="7" t="inlineStr">
         <is>
@@ -15348,7 +15348,7 @@
         <v>0</v>
       </c>
       <c r="V151" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W151" s="9" t="n">
         <v>0</v>
@@ -15483,7 +15483,7 @@
         </is>
       </c>
       <c r="E153" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F153" s="6" t="n">
         <v>10</v>
@@ -15497,17 +15497,17 @@
         </is>
       </c>
       <c r="I153" s="4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J153" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K153" s="4" t="n">
-        <v>-3</v>
-      </c>
-      <c r="L153" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>-2</v>
+      </c>
+      <c r="L153" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M153" s="8" t="n">
@@ -15538,11 +15538,11 @@
       <c r="T153" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U153" s="9" t="n">
-        <v>0</v>
+      <c r="U153" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V153" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W153" s="9" t="n">
         <v>0</v>
@@ -16038,7 +16038,7 @@
         <v>6</v>
       </c>
       <c r="D5" t="n">
-        <v>2</v>
+        <v>2.17</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -16203,7 +16203,7 @@
         <v>5</v>
       </c>
       <c r="D10" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -16434,7 +16434,7 @@
         <v>6</v>
       </c>
       <c r="D17" t="n">
-        <v>2</v>
+        <v>2.17</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -16449,7 +16449,7 @@
         <v>0</v>
       </c>
       <c r="I17" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="18">
@@ -16500,7 +16500,7 @@
         <v>6</v>
       </c>
       <c r="D19" t="n">
-        <v>2.33</v>
+        <v>2.5</v>
       </c>
       <c r="E19" t="n">
         <v>1</v>
@@ -16533,7 +16533,7 @@
         <v>5</v>
       </c>
       <c r="D20" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="E20" t="n">
         <v>1</v>
@@ -16566,7 +16566,7 @@
         <v>5</v>
       </c>
       <c r="D21" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
@@ -16632,7 +16632,7 @@
         <v>4</v>
       </c>
       <c r="D23" t="n">
-        <v>2.25</v>
+        <v>2.5</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
@@ -16665,7 +16665,7 @@
         <v>5</v>
       </c>
       <c r="D24" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="E24" t="n">
         <v>1</v>
@@ -16680,7 +16680,7 @@
         <v>0</v>
       </c>
       <c r="I24" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="25">
@@ -16698,13 +16698,13 @@
         <v>5</v>
       </c>
       <c r="D25" t="n">
-        <v>2.4</v>
+        <v>3.2</v>
       </c>
       <c r="E25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F25" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
@@ -16863,7 +16863,7 @@
         <v>5</v>
       </c>
       <c r="D30" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="E30" t="n">
         <v>0</v>
@@ -16878,7 +16878,7 @@
         <v>0</v>
       </c>
       <c r="I30" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
